--- a/database/event/3190/event_3190_evp_summary.xlsx
+++ b/database/event/3190/event_3190_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.6931</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6102</v>
+        <v>2.5458</v>
       </c>
       <c r="E2" t="n">
         <v>7.5044</v>
@@ -548,7 +548,7 @@
         <v>0.4344</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4788</v>
+        <v>1.43</v>
       </c>
       <c r="E3" t="n">
         <v>4.7036</v>
@@ -594,7 +594,7 @@
         <v>0.4285</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4529</v>
+        <v>1.4044</v>
       </c>
       <c r="E4" t="n">
         <v>4.6394</v>
@@ -640,7 +640,7 @@
         <v>0.4196</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4139</v>
+        <v>1.3661</v>
       </c>
       <c r="E5" t="n">
         <v>4.5431</v>
@@ -686,7 +686,7 @@
         <v>0.3413</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0714</v>
+        <v>1.0282</v>
       </c>
       <c r="E6" t="n">
         <v>3.6951</v>
@@ -732,7 +732,7 @@
         <v>0.3046</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9112</v>
+        <v>0.8702</v>
       </c>
       <c r="E7" t="n">
         <v>3.2985</v>
@@ -778,7 +778,7 @@
         <v>0.2941</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8652</v>
+        <v>0.8249</v>
       </c>
       <c r="E8" t="n">
         <v>3.1848</v>
@@ -824,7 +824,7 @@
         <v>0.2789</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7987</v>
+        <v>0.7593</v>
       </c>
       <c r="E9" t="n">
         <v>3.0202</v>
@@ -870,7 +870,7 @@
         <v>0.2581</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7076</v>
+        <v>0.6695</v>
       </c>
       <c r="E10" t="n">
         <v>2.7947</v>
@@ -916,7 +916,7 @@
         <v>0.2361</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6115</v>
+        <v>0.5747</v>
       </c>
       <c r="E11" t="n">
         <v>2.5568</v>
@@ -962,7 +962,7 @@
         <v>0.233</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5978</v>
+        <v>0.5612</v>
       </c>
       <c r="E12" t="n">
         <v>2.5228</v>
@@ -1008,7 +1008,7 @@
         <v>0.2225</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5517</v>
+        <v>0.5157</v>
       </c>
       <c r="E13" t="n">
         <v>2.4086</v>
@@ -1054,7 +1054,7 @@
         <v>0.2214</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5471</v>
+        <v>0.5112</v>
       </c>
       <c r="E14" t="n">
         <v>2.3974</v>
@@ -1100,7 +1100,7 @@
         <v>0.2092</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4935</v>
+        <v>0.4583</v>
       </c>
       <c r="E15" t="n">
         <v>2.2646</v>
@@ -1146,7 +1146,7 @@
         <v>0.1703</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3234</v>
+        <v>0.2905</v>
       </c>
       <c r="E16" t="n">
         <v>1.8435</v>
@@ -1192,7 +1192,7 @@
         <v>0.1667</v>
       </c>
       <c r="D17" t="n">
-        <v>0.308</v>
+        <v>0.2754</v>
       </c>
       <c r="E17" t="n">
         <v>1.8054</v>
@@ -1238,7 +1238,7 @@
         <v>0.155</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2566</v>
+        <v>0.2247</v>
       </c>
       <c r="E18" t="n">
         <v>1.6782</v>
@@ -1284,7 +1284,7 @@
         <v>0.149</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2306</v>
+        <v>0.199</v>
       </c>
       <c r="E19" t="n">
         <v>1.6138</v>
@@ -1330,7 +1330,7 @@
         <v>0.1355</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1714</v>
+        <v>0.1407</v>
       </c>
       <c r="E20" t="n">
         <v>1.4674</v>
@@ -1376,7 +1376,7 @@
         <v>0.1344</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1667</v>
+        <v>0.136</v>
       </c>
       <c r="E21" t="n">
         <v>1.4556</v>
@@ -1422,7 +1422,7 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0664</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>0.8787</v>
@@ -1468,7 +1468,7 @@
         <v>0.0761</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.1155</v>
       </c>
       <c r="E23" t="n">
         <v>0.8242</v>
@@ -1514,7 +1514,7 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1278</v>
+        <v>-0.1544</v>
       </c>
       <c r="E24" t="n">
         <v>0.7266</v>
@@ -1560,7 +1560,7 @@
         <v>0.0566</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1739</v>
+        <v>-0.1999</v>
       </c>
       <c r="E25" t="n">
         <v>0.6126</v>
@@ -1606,7 +1606,7 @@
         <v>0.0519</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1944</v>
+        <v>-0.2201</v>
       </c>
       <c r="E26" t="n">
         <v>0.5617</v>
@@ -1652,7 +1652,7 @@
         <v>0.0514</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1966</v>
+        <v>-0.2222</v>
       </c>
       <c r="E27" t="n">
         <v>0.5564</v>
@@ -1698,7 +1698,7 @@
         <v>0.0494</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2052</v>
+        <v>-0.2307</v>
       </c>
       <c r="E28" t="n">
         <v>0.5352</v>
@@ -1744,7 +1744,7 @@
         <v>0.0461</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2196</v>
+        <v>-0.2449</v>
       </c>
       <c r="E29" t="n">
         <v>0.4994</v>
@@ -1790,7 +1790,7 @@
         <v>0.0062</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3941</v>
+        <v>-0.417</v>
       </c>
       <c r="E30" t="n">
         <v>0.0675</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0094</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4624</v>
+        <v>-0.4844</v>
       </c>
       <c r="E31" t="n">
         <v>-0.1016</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0214</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.515</v>
+        <v>-0.5363</v>
       </c>
       <c r="E32" t="n">
         <v>-0.2319</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0226</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5203</v>
+        <v>-0.5415</v>
       </c>
       <c r="E33" t="n">
         <v>-0.245</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0333</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5876</v>
       </c>
       <c r="E34" t="n">
         <v>-0.3606</v>
@@ -2020,7 +2020,7 @@
         <v>-0.0813</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7769</v>
+        <v>-0.7945</v>
       </c>
       <c r="E35" t="n">
         <v>-0.88</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1089</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8979</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1795</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1255</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9704</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3591</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1286</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9838</v>
+        <v>-0.9986</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3922</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2459</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4971</v>
+        <v>-1.5048</v>
       </c>
       <c r="E39" t="n">
         <v>-2.6629</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2558</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5401</v>
+        <v>-1.5472</v>
       </c>
       <c r="E40" t="n">
         <v>-2.7694</v>
@@ -2296,7 +2296,7 @@
         <v>-0.2599</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5582</v>
+        <v>-1.565</v>
       </c>
       <c r="E41" t="n">
         <v>-2.814</v>

--- a/database/event/3190/event_3190_evp_summary.xlsx
+++ b/database/event/3190/event_3190_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5044</v>
+        <v>6.6483</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6931</v>
+        <v>0.614</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5458</v>
+        <v>2.3634</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5044</v>
+        <v>6.6483</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3404</v>
+        <v>3.939</v>
       </c>
       <c r="G2" t="n">
-        <v>3.164</v>
+        <v>2.7093</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9021</v>
+        <v>8.392099999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9733</v>
+        <v>4.3635</v>
       </c>
       <c r="J2" t="n">
-        <v>3.164</v>
+        <v>2.7093</v>
       </c>
       <c r="K2" t="n">
         <v>160</v>
@@ -529,7 +529,7 @@
         <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1373</v>
+        <v>7.0728</v>
       </c>
       <c r="N2" t="n">
         <v>291</v>
@@ -538,47 +538,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7036</v>
+        <v>4.3227</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4344</v>
+        <v>0.3992</v>
       </c>
       <c r="D3" t="n">
-        <v>1.43</v>
+        <v>1.3135</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7036</v>
+        <v>4.3227</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0199</v>
+        <v>4.1822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6837</v>
+        <v>0.1405</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0199</v>
+        <v>9.2491</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2582</v>
+        <v>4.8091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6837</v>
+        <v>0.1405</v>
       </c>
       <c r="K3" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="L3" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9419</v>
+        <v>4.9496</v>
       </c>
       <c r="N3" t="n">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6394</v>
+        <v>4.0533</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4285</v>
+        <v>0.3744</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4044</v>
+        <v>1.1918</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6394</v>
+        <v>4.0533</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1712</v>
+        <v>3.5716</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4682</v>
+        <v>0.4817</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2211</v>
+        <v>7.0977</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4213</v>
+        <v>3.6905</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4682</v>
+        <v>0.4817</v>
       </c>
       <c r="K4" t="n">
         <v>194</v>
@@ -621,7 +621,7 @@
         <v>81</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8895</v>
+        <v>4.1722</v>
       </c>
       <c r="N4" t="n">
         <v>275</v>
@@ -630,265 +630,265 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5431</v>
+        <v>3.9948</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4196</v>
+        <v>0.369</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3661</v>
+        <v>1.1654</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5431</v>
+        <v>3.9948</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4194</v>
+        <v>3.4534</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1237</v>
+        <v>0.5414</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2199</v>
+        <v>6.6813</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2309</v>
+        <v>3.474</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1237</v>
+        <v>0.5414</v>
       </c>
       <c r="K5" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="L5" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3546</v>
+        <v>4.015400000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6951</v>
+        <v>3.8566</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3413</v>
+        <v>0.3562</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0282</v>
+        <v>1.103</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6951</v>
+        <v>3.8566</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5117</v>
+        <v>2.3873</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1834</v>
+        <v>1.4693</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5117</v>
+        <v>2.9249</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8463</v>
+        <v>1.5208</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1834</v>
+        <v>1.4693</v>
       </c>
       <c r="K6" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0297</v>
+        <v>2.9901</v>
       </c>
       <c r="N6" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2985</v>
+        <v>3.7473</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3046</v>
+        <v>0.3461</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8702</v>
+        <v>1.0537</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2985</v>
+        <v>3.7473</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6494</v>
+        <v>2.7247</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6491</v>
+        <v>1.0226</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6494</v>
+        <v>4.1138</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1474</v>
+        <v>2.139</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6491</v>
+        <v>1.0226</v>
       </c>
       <c r="K7" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="L7" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7965</v>
+        <v>3.1616</v>
       </c>
       <c r="N7" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1848</v>
+        <v>3.7399</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2941</v>
+        <v>0.3454</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8249</v>
+        <v>1.0504</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1848</v>
+        <v>3.7399</v>
       </c>
       <c r="F8" t="n">
-        <v>2.195</v>
+        <v>3.1401</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9898</v>
+        <v>0.5998</v>
       </c>
       <c r="H8" t="n">
-        <v>2.195</v>
+        <v>5.5775</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7791</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9898</v>
+        <v>0.5998</v>
       </c>
       <c r="K8" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="L8" t="n">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7689</v>
+        <v>3.4998</v>
       </c>
       <c r="N8" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0202</v>
+        <v>3.536</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2789</v>
+        <v>0.3266</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7593</v>
+        <v>0.9583</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0202</v>
+        <v>3.536</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0876</v>
+        <v>3.3074</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1078</v>
+        <v>0.2286</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0876</v>
+        <v>6.167</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07099999999999999</v>
+        <v>3.2066</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1078</v>
+        <v>0.2286</v>
       </c>
       <c r="K9" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="L9" t="n">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0368</v>
+        <v>3.4352</v>
       </c>
       <c r="N9" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7947</v>
+        <v>3.5145</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2581</v>
+        <v>0.3246</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6695</v>
+        <v>0.9486</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7947</v>
+        <v>3.5145</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1525</v>
+        <v>0.5602</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6422</v>
+        <v>2.9543</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1525</v>
+        <v>0.5602</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9342</v>
+        <v>0.2913</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6422</v>
+        <v>2.9543</v>
       </c>
       <c r="K10" t="n">
         <v>160</v>
@@ -897,7 +897,7 @@
         <v>131</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5764</v>
+        <v>3.2456</v>
       </c>
       <c r="N10" t="n">
         <v>291</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5568</v>
+        <v>3.1178</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2361</v>
+        <v>0.288</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5747</v>
+        <v>0.7695</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5568</v>
+        <v>3.1178</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9896</v>
+        <v>2.7864</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4328</v>
+        <v>0.3314</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9896</v>
+        <v>4.3312</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2337</v>
+        <v>2.252</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4328</v>
+        <v>0.3314</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>211</v>
       </c>
       <c r="L11" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8009</v>
+        <v>2.5834</v>
       </c>
       <c r="N11" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5228</v>
+        <v>2.817</v>
       </c>
       <c r="C12" t="n">
-        <v>0.233</v>
+        <v>0.2602</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5612</v>
+        <v>0.6337</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5228</v>
+        <v>2.817</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4771</v>
+        <v>2.832</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9543</v>
+        <v>-0.015</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4771</v>
+        <v>4.4918</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8182</v>
+        <v>2.3356</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9543</v>
+        <v>-0.015</v>
       </c>
       <c r="K12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8639</v>
+        <v>2.3206</v>
       </c>
       <c r="N12" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4086</v>
+        <v>2.7118</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2225</v>
+        <v>0.2505</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5157</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4086</v>
+        <v>2.7118</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7551</v>
+        <v>2.7854</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3465</v>
+        <v>-0.0736</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7551</v>
+        <v>4.3277</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2331</v>
+        <v>2.2502</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3465</v>
+        <v>-0.0736</v>
       </c>
       <c r="K13" t="n">
         <v>132</v>
@@ -1035,7 +1035,7 @@
         <v>103</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8866</v>
+        <v>2.1766</v>
       </c>
       <c r="N13" t="n">
         <v>235</v>
@@ -1044,630 +1044,630 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3974</v>
+        <v>2.5887</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2214</v>
+        <v>0.2391</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5112</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3974</v>
+        <v>2.5887</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5259</v>
+        <v>3.2138</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1285</v>
+        <v>-0.6251</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5259</v>
+        <v>5.8372</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0473</v>
+        <v>3.0351</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1285</v>
+        <v>-0.6251</v>
       </c>
       <c r="K14" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="L14" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9188</v>
+        <v>2.41</v>
       </c>
       <c r="N14" t="n">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2646</v>
+        <v>2.5728</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2092</v>
+        <v>0.2376</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4583</v>
+        <v>0.5235</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2646</v>
+        <v>2.5728</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0107</v>
+        <v>2.5728</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2539</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0107</v>
+        <v>2.5728</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6297</v>
+        <v>2.5728</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2539</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8836</v>
+        <v>2.5728</v>
       </c>
       <c r="N15" t="n">
-        <v>264</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8435</v>
+        <v>2.524</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1703</v>
+        <v>0.2331</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2905</v>
+        <v>0.5014</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8435</v>
+        <v>2.524</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8435</v>
+        <v>3.5999</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-1.0759</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8435</v>
+        <v>7.1976</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8435</v>
+        <v>3.7424</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-1.0759</v>
       </c>
       <c r="K16" t="n">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8435</v>
+        <v>2.6665</v>
       </c>
       <c r="N16" t="n">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8054</v>
+        <v>2.0743</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1667</v>
+        <v>0.1916</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2754</v>
+        <v>0.2984</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8054</v>
+        <v>2.0743</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8054</v>
+        <v>2.0743</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8054</v>
+        <v>2.0743</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8054</v>
+        <v>2.0743</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8054</v>
+        <v>2.0743</v>
       </c>
       <c r="N17" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6782</v>
+        <v>2.0462</v>
       </c>
       <c r="C18" t="n">
-        <v>0.155</v>
+        <v>0.189</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2247</v>
+        <v>0.2857</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6782</v>
+        <v>2.0462</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6782</v>
+        <v>2.0462</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6782</v>
+        <v>2.0462</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6782</v>
+        <v>2.0462</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>241</v>
+        <v>165</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6782</v>
+        <v>2.0462</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6138</v>
+        <v>1.9729</v>
       </c>
       <c r="C19" t="n">
-        <v>0.149</v>
+        <v>0.1822</v>
       </c>
       <c r="D19" t="n">
-        <v>0.199</v>
+        <v>0.2527</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6138</v>
+        <v>1.9729</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6138</v>
+        <v>1.9729</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6138</v>
+        <v>1.9729</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6138</v>
+        <v>1.9729</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>165</v>
+        <v>241</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6138</v>
+        <v>1.9729</v>
       </c>
       <c r="N19" t="n">
-        <v>165</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4674</v>
+        <v>1.8674</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1355</v>
+        <v>0.1725</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1407</v>
+        <v>0.205</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4674</v>
+        <v>1.8674</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4674</v>
+        <v>1.8674</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4674</v>
+        <v>1.8674</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4674</v>
+        <v>1.8674</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4674</v>
+        <v>1.8674</v>
       </c>
       <c r="N20" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4556</v>
+        <v>1.7051</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1344</v>
+        <v>0.1575</v>
       </c>
       <c r="D21" t="n">
-        <v>0.136</v>
+        <v>0.1318</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4556</v>
+        <v>1.7051</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4556</v>
+        <v>2.3341</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.629</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4556</v>
+        <v>2.7377</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4556</v>
+        <v>1.4235</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.629</v>
       </c>
       <c r="K21" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4556</v>
+        <v>0.7945</v>
       </c>
       <c r="N21" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8787</v>
+        <v>1.6891</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.1245</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8787</v>
+        <v>1.6891</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2486</v>
+        <v>1.6891</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1273</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2486</v>
+        <v>1.6891</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.012</v>
+        <v>1.6891</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1273</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="L22" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1153</v>
+        <v>1.6891</v>
       </c>
       <c r="N22" t="n">
-        <v>235</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8242</v>
+        <v>1.378</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0761</v>
+        <v>0.1273</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1155</v>
+        <v>-0.0159</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8242</v>
+        <v>1.378</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8242</v>
+        <v>2.1928</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.8148</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8242</v>
+        <v>2.2396</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8242</v>
+        <v>1.1645</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.8148</v>
       </c>
       <c r="K23" t="n">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8242</v>
+        <v>0.3497000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>175</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>COLDYY1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7266</v>
+        <v>1.3552</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.1252</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1544</v>
+        <v>-0.0262</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7266</v>
+        <v>1.3552</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2294</v>
+        <v>1.3552</v>
       </c>
       <c r="G24" t="n">
-        <v>0.956</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2294</v>
+        <v>1.3552</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1859</v>
+        <v>1.3552</v>
       </c>
       <c r="J24" t="n">
-        <v>0.956</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="L24" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7701</v>
+        <v>1.3552</v>
       </c>
       <c r="N24" t="n">
-        <v>235</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6126</v>
+        <v>1.2175</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0566</v>
+        <v>0.1124</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1999</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6126</v>
+        <v>1.2175</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6126</v>
+        <v>0.3535</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.864</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6126</v>
+        <v>0.3535</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6126</v>
+        <v>0.1838</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.864</v>
       </c>
       <c r="K25" t="n">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6126</v>
+        <v>1.0478</v>
       </c>
       <c r="N25" t="n">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dimaoneshot</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5617</v>
+        <v>1.208</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0519</v>
+        <v>0.1116</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2201</v>
+        <v>-0.0927</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5617</v>
+        <v>1.208</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5617</v>
+        <v>1.208</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5617</v>
+        <v>1.208</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5617</v>
+        <v>1.208</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5617</v>
+        <v>1.208</v>
       </c>
       <c r="N26" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COLDYY1</t>
+          <t>Dimaoneshot</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5564</v>
+        <v>1.106</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0514</v>
+        <v>0.1021</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2222</v>
+        <v>-0.1387</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5564</v>
+        <v>1.106</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5564</v>
+        <v>1.106</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5564</v>
+        <v>1.106</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5564</v>
+        <v>1.106</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5564</v>
+        <v>1.106</v>
       </c>
       <c r="N27" t="n">
         <v>182</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KHRN</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5352</v>
+        <v>1.0842</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0494</v>
+        <v>0.1001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2307</v>
+        <v>-0.1486</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5352</v>
+        <v>1.0842</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5352</v>
+        <v>1.0842</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5352</v>
+        <v>1.0842</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5352</v>
+        <v>1.0842</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5352</v>
+        <v>1.0842</v>
       </c>
       <c r="N28" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>KHRN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4994</v>
+        <v>1.0067</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0461</v>
+        <v>0.093</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2449</v>
+        <v>-0.1835</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4994</v>
+        <v>1.0067</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4749</v>
+        <v>1.0067</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9755</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4749</v>
+        <v>1.0067</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1955</v>
+        <v>1.0067</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9755</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="L29" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.22</v>
+        <v>1.0067</v>
       </c>
       <c r="N29" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0675</v>
+        <v>0.5376</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0062</v>
+        <v>0.0497</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.417</v>
+        <v>-0.3953</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0675</v>
+        <v>0.5376</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.1004</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8957000000000001</v>
+        <v>0.4372</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.1004</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.0522</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8957000000000001</v>
+        <v>0.4372</v>
       </c>
       <c r="K30" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="L30" t="n">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1150000000000001</v>
+        <v>0.4894</v>
       </c>
       <c r="N30" t="n">
-        <v>235</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1016</v>
+        <v>0.3813</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0094</v>
+        <v>0.0352</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4844</v>
+        <v>-0.4659</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1016</v>
+        <v>0.3813</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1016</v>
+        <v>0.3813</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1016</v>
+        <v>0.3813</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1016</v>
+        <v>0.3813</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1016</v>
+        <v>0.3813</v>
       </c>
       <c r="N31" t="n">
         <v>165</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2319</v>
+        <v>0.2771</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0214</v>
+        <v>0.0256</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5363</v>
+        <v>-0.5129</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2319</v>
+        <v>0.2771</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2319</v>
+        <v>-1.3438</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.6209</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2319</v>
+        <v>-1.3438</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2319</v>
+        <v>-0.6987</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.6209</v>
       </c>
       <c r="K32" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2319</v>
+        <v>0.9222</v>
       </c>
       <c r="N32" t="n">
-        <v>165</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.245</v>
+        <v>0.0859</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0226</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5415</v>
+        <v>-0.5992</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.245</v>
+        <v>0.0859</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2633</v>
+        <v>0.0859</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0183</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2633</v>
+        <v>0.0859</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2134</v>
+        <v>0.0859</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0183</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="L33" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1951</v>
+        <v>0.0859</v>
       </c>
       <c r="N33" t="n">
-        <v>291</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3606</v>
+        <v>0.0369</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0333</v>
+        <v>0.0034</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5876</v>
+        <v>-0.6214</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3606</v>
+        <v>0.0369</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3606</v>
+        <v>0.0369</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3606</v>
+        <v>0.0369</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3606</v>
+        <v>0.0369</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3606</v>
+        <v>0.0369</v>
       </c>
       <c r="N34" t="n">
         <v>175</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.88</v>
+        <v>0.0056</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0813</v>
+        <v>0.0005</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7945</v>
+        <v>-0.6355</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.88</v>
+        <v>0.0056</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3275</v>
+        <v>0.3437</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5525</v>
+        <v>-0.3381</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3275</v>
+        <v>0.3437</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2655</v>
+        <v>0.1787</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5525</v>
+        <v>-0.3381</v>
       </c>
       <c r="K35" t="n">
         <v>194</v>
@@ -2047,7 +2047,7 @@
         <v>81</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8180000000000001</v>
+        <v>-0.1594</v>
       </c>
       <c r="N35" t="n">
         <v>275</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1795</v>
+        <v>-0.4245</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1089</v>
+        <v>-0.0392</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.8297</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1795</v>
+        <v>-0.4245</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1795</v>
+        <v>-0.4245</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1795</v>
+        <v>-0.4245</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1795</v>
+        <v>-0.4245</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1795</v>
+        <v>-0.4245</v>
       </c>
       <c r="N36" t="n">
         <v>241</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3591</v>
+        <v>-0.7986</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1255</v>
+        <v>-0.0738</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3591</v>
+        <v>-0.7986</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3591</v>
+        <v>-0.7986</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3591</v>
+        <v>-0.7986</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3591</v>
+        <v>-0.7986</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3591</v>
+        <v>-0.7986</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3922</v>
+        <v>-0.862</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1286</v>
+        <v>-0.0796</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9986</v>
+        <v>-1.0272</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3922</v>
+        <v>-0.862</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3922</v>
+        <v>-0.862</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3922</v>
+        <v>-0.862</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3922</v>
+        <v>-0.862</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3922</v>
+        <v>-0.862</v>
       </c>
       <c r="N38" t="n">
         <v>182</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.6629</v>
+        <v>-1.8346</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2459</v>
+        <v>-0.1694</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.5048</v>
+        <v>-1.4662</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.6629</v>
+        <v>-1.8346</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.6629</v>
+        <v>-1.8346</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.6629</v>
+        <v>-1.8346</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.6629</v>
+        <v>-1.8346</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.6629</v>
+        <v>-1.8346</v>
       </c>
       <c r="N39" t="n">
         <v>241</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.7694</v>
+        <v>-2.0821</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2558</v>
+        <v>-0.1923</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5472</v>
+        <v>-1.578</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.7694</v>
+        <v>-2.0821</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.7694</v>
+        <v>-2.0821</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.7694</v>
+        <v>-2.0821</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.7694</v>
+        <v>-2.0821</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.7694</v>
+        <v>-2.0821</v>
       </c>
       <c r="N40" t="n">
         <v>182</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.814</v>
+        <v>-2.2396</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2599</v>
+        <v>-0.2068</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.565</v>
+        <v>-1.6491</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.814</v>
+        <v>-2.2396</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.814</v>
+        <v>-2.2396</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.814</v>
+        <v>-2.2396</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.814</v>
+        <v>-2.2396</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.814</v>
+        <v>-2.2396</v>
       </c>
       <c r="N41" t="n">
         <v>182</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3116</v>
+        <v>0.3305</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4784</v>
+        <v>7.932</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.96</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0196</v>
+        <v>-0.042</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4704</v>
+        <v>-1.008</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1692</v>
+        <v>-0.1378</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.0608</v>
+        <v>-3.3072</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4786</v>
+        <v>-0.3142</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.4864</v>
+        <v>-7.5408</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7635</v>
+        <v>-0.5191</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.324</v>
+        <v>-12.4584</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.123</v>
+        <v>1.0864</v>
       </c>
       <c r="J7" t="n">
-        <v>26.952</v>
+        <v>26.0736</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0605</v>
+        <v>1.0478</v>
       </c>
       <c r="J8" t="n">
-        <v>25.452</v>
+        <v>25.1472</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.9079</v>
       </c>
       <c r="J9" t="n">
-        <v>21.2544</v>
+        <v>21.7896</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3379</v>
+        <v>0.4199</v>
       </c>
       <c r="J10" t="n">
-        <v>8.1096</v>
+        <v>10.0776</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2854</v>
+        <v>-0.201</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.8496</v>
+        <v>-4.824</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>0.645</v>
+        <v>0.7865</v>
       </c>
       <c r="J12" t="n">
-        <v>16.77</v>
+        <v>20.449</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2199</v>
+        <v>-0.1378</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.7174</v>
+        <v>-3.5828</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2376</v>
+        <v>-0.1485</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.1776</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4098</v>
+        <v>-0.2606</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.6548</v>
+        <v>-6.7756</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4522</v>
+        <v>-0.2898</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.7572</v>
+        <v>-7.5348</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>1.45</v>
+        <v>1.2888</v>
       </c>
       <c r="J17" t="n">
-        <v>37.7</v>
+        <v>33.5088</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7126</v>
+        <v>0.708</v>
       </c>
       <c r="J18" t="n">
-        <v>18.5276</v>
+        <v>18.408</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3098</v>
+        <v>0.364</v>
       </c>
       <c r="J19" t="n">
-        <v>8.0548</v>
+        <v>9.464</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.062</v>
+        <v>0.1262</v>
       </c>
       <c r="J20" t="n">
-        <v>1.612</v>
+        <v>3.2812</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6502</v>
+        <v>-0.5898</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.9052</v>
+        <v>-15.3348</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.33</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5516</v>
+        <v>0.6605</v>
       </c>
       <c r="J22" t="n">
-        <v>16.548</v>
+        <v>19.815</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.11</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2363</v>
+        <v>0.2612</v>
       </c>
       <c r="J23" t="n">
-        <v>7.089</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.97</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1018</v>
+        <v>-0.0521</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.054</v>
+        <v>-1.563</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1234</v>
+        <v>-0.0654</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.702</v>
+        <v>-1.962</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.74</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4715</v>
+        <v>-0.3005</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.145</v>
+        <v>-9.015000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9665</v>
+        <v>0.959</v>
       </c>
       <c r="J27" t="n">
-        <v>28.995</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9225</v>
+        <v>0.917</v>
       </c>
       <c r="J28" t="n">
-        <v>27.675</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.14</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3697</v>
+        <v>0.4173</v>
       </c>
       <c r="J29" t="n">
-        <v>11.091</v>
+        <v>12.519</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.08</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1919</v>
+        <v>0.252</v>
       </c>
       <c r="J30" t="n">
-        <v>5.757</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4388</v>
+        <v>-0.3666</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.164</v>
+        <v>-10.998</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.4</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6187</v>
+        <v>0.7548</v>
       </c>
       <c r="J32" t="n">
-        <v>22.2732</v>
+        <v>27.1728</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3092</v>
+        <v>0.3614</v>
       </c>
       <c r="J33" t="n">
-        <v>11.1312</v>
+        <v>13.0104</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1463</v>
+        <v>0.1908</v>
       </c>
       <c r="J34" t="n">
-        <v>5.2668</v>
+        <v>6.8688</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1225</v>
+        <v>-0.0584</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.41</v>
+        <v>-2.1024</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4009</v>
+        <v>-0.2484</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.4324</v>
+        <v>-8.942399999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.35</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0014</v>
+        <v>0.9744</v>
       </c>
       <c r="J37" t="n">
-        <v>36.0504</v>
+        <v>35.0784</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.348</v>
+        <v>0.3115</v>
       </c>
       <c r="J38" t="n">
-        <v>12.528</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2862</v>
+        <v>-0.2361</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.3032</v>
+        <v>-8.499599999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.9</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4101</v>
+        <v>-0.3563</v>
       </c>
       <c r="J40" t="n">
-        <v>-14.7636</v>
+        <v>-12.8268</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5493</v>
+        <v>-0.4962</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.7748</v>
+        <v>-17.8632</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2967</v>
+        <v>0.3205</v>
       </c>
       <c r="J42" t="n">
-        <v>8.901</v>
+        <v>9.615</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2132</v>
+        <v>0.2186</v>
       </c>
       <c r="J43" t="n">
-        <v>6.396</v>
+        <v>6.558</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0302</v>
+        <v>-0.0321</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.906</v>
+        <v>-0.963</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3095</v>
+        <v>-0.1922</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.285</v>
+        <v>-5.766</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4968</v>
+        <v>-0.3206</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.904</v>
+        <v>-9.618</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.966</v>
+        <v>0.7002</v>
       </c>
       <c r="J47" t="n">
-        <v>28.98</v>
+        <v>21.006</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.23</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6641</v>
+        <v>0.5191</v>
       </c>
       <c r="J48" t="n">
-        <v>19.923</v>
+        <v>15.573</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4776</v>
+        <v>0.4166</v>
       </c>
       <c r="J49" t="n">
-        <v>14.328</v>
+        <v>12.498</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3031</v>
+        <v>-0.2323</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.093</v>
+        <v>-6.969</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3031</v>
+        <v>-0.2323</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.093</v>
+        <v>-6.969</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6875</v>
+        <v>0.4968</v>
       </c>
       <c r="J52" t="n">
-        <v>18.5625</v>
+        <v>13.4136</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.32</v>
       </c>
       <c r="I53" t="n">
-        <v>0.478</v>
+        <v>0.3849</v>
       </c>
       <c r="J53" t="n">
-        <v>12.906</v>
+        <v>10.3923</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.25</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3801</v>
+        <v>0.3348</v>
       </c>
       <c r="J54" t="n">
-        <v>10.2627</v>
+        <v>9.0396</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.04</v>
       </c>
       <c r="I55" t="n">
-        <v>0.026</v>
+        <v>0.0585</v>
       </c>
       <c r="J55" t="n">
-        <v>0.702</v>
+        <v>1.5795</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1722</v>
+        <v>-0.0847</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.6494</v>
+        <v>-2.2869</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3787</v>
+        <v>0.3235</v>
       </c>
       <c r="J57" t="n">
-        <v>10.2249</v>
+        <v>8.734500000000001</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.97</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0459</v>
+        <v>-0.0445</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.2393</v>
+        <v>-1.2015</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0905</v>
+        <v>-0.0704</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.4435</v>
+        <v>-1.9008</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3658</v>
+        <v>-0.2308</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.8766</v>
+        <v>-6.2316</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4241</v>
+        <v>-0.2704</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.4507</v>
+        <v>-7.3008</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.84</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.217</v>
+        <v>-0.174</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.208</v>
+        <v>-4.176</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.269</v>
+        <v>-0.2044</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.456</v>
+        <v>-4.9056</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3065</v>
+        <v>-0.2237</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.356</v>
+        <v>-5.3688</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.79</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3065</v>
+        <v>-0.2237</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.356</v>
+        <v>-5.3688</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4784</v>
+        <v>-0.3177</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.4816</v>
+        <v>-7.6248</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.79</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7181</v>
+        <v>1.2063</v>
       </c>
       <c r="J67" t="n">
-        <v>41.2344</v>
+        <v>28.9512</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.5429</v>
       </c>
       <c r="J68" t="n">
-        <v>15.06</v>
+        <v>13.0296</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3405</v>
+        <v>0.3855</v>
       </c>
       <c r="J69" t="n">
-        <v>8.172000000000001</v>
+        <v>9.252000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2873</v>
+        <v>0.3542</v>
       </c>
       <c r="J70" t="n">
-        <v>6.8952</v>
+        <v>8.5008</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.011</v>
+        <v>0.0669</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.264</v>
+        <v>1.6056</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1202</v>
+        <v>0.7921</v>
       </c>
       <c r="J72" t="n">
-        <v>33.606</v>
+        <v>23.763</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8094</v>
+        <v>0.5916</v>
       </c>
       <c r="J73" t="n">
-        <v>24.282</v>
+        <v>17.748</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.5405</v>
+        <v>-0.4902</v>
       </c>
       <c r="J74" t="n">
-        <v>-16.215</v>
+        <v>-14.706</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.79</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6947</v>
+        <v>-0.6489</v>
       </c>
       <c r="J75" t="n">
-        <v>-20.841</v>
+        <v>-19.467</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.73</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8383</v>
+        <v>-0.8012</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.149</v>
+        <v>-24.036</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5342</v>
       </c>
       <c r="J77" t="n">
-        <v>16.617</v>
+        <v>16.026</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.32</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5029</v>
+        <v>0.4956</v>
       </c>
       <c r="J78" t="n">
-        <v>15.087</v>
+        <v>14.868</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0034</v>
+        <v>0.0452</v>
       </c>
       <c r="J79" t="n">
-        <v>0.102</v>
+        <v>1.356</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0553</v>
+        <v>-0.0122</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.659</v>
+        <v>-0.366</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.97</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1356</v>
+        <v>-0.0635</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.068</v>
+        <v>-1.905</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.79</v>
       </c>
       <c r="I82" t="n">
-        <v>1.733</v>
+        <v>1.2198</v>
       </c>
       <c r="J82" t="n">
-        <v>39.859</v>
+        <v>28.0554</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.799</v>
+        <v>0.6138</v>
       </c>
       <c r="J83" t="n">
-        <v>18.377</v>
+        <v>14.1174</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3346</v>
+        <v>0.3759</v>
       </c>
       <c r="J84" t="n">
-        <v>7.6958</v>
+        <v>8.6457</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.104</v>
+        <v>0.1773</v>
       </c>
       <c r="J85" t="n">
-        <v>2.392</v>
+        <v>4.0779</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.64</v>
+        <v>-0.5768</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.72</v>
+        <v>-13.2664</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.08</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2387</v>
+        <v>0.2408</v>
       </c>
       <c r="J87" t="n">
-        <v>5.4901</v>
+        <v>5.5384</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.02</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1203</v>
+        <v>0.0953</v>
       </c>
       <c r="J88" t="n">
-        <v>2.7669</v>
+        <v>2.1919</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.01</v>
       </c>
       <c r="I89" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>2.1896</v>
+        <v>1.5088</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.249</v>
+        <v>-0.1642</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.727</v>
+        <v>-3.7766</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.44</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8187</v>
+        <v>-0.5616</v>
       </c>
       <c r="J91" t="n">
-        <v>-18.8301</v>
+        <v>-12.9168</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.403</v>
+        <v>0.4526</v>
       </c>
       <c r="J92" t="n">
-        <v>10.075</v>
+        <v>11.315</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2073</v>
+        <v>-0.1596</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.1825</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2257</v>
+        <v>-0.1698</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.6425</v>
+        <v>-4.245</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3264</v>
+        <v>-0.2184</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.16</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.47</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7761</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-19.4025</v>
+        <v>-13.2175</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.53</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2604</v>
+        <v>1.1691</v>
       </c>
       <c r="J97" t="n">
-        <v>31.51</v>
+        <v>29.2275</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8822</v>
+        <v>0.8946</v>
       </c>
       <c r="J98" t="n">
-        <v>22.055</v>
+        <v>22.365</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.35</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8822</v>
+        <v>0.8946</v>
       </c>
       <c r="J99" t="n">
-        <v>22.055</v>
+        <v>22.365</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4599</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>11.4975</v>
+        <v>13.2175</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7401</v>
+        <v>-0.6853</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.5025</v>
+        <v>-17.1325</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5291</v>
+        <v>0.6264</v>
       </c>
       <c r="J102" t="n">
-        <v>11.6402</v>
+        <v>13.7808</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0425</v>
+        <v>-0.0564</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-1.2408</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.227</v>
+        <v>-0.1701</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.994</v>
+        <v>-3.7422</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4372</v>
+        <v>-0.2863</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.618399999999999</v>
+        <v>-6.2986</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.37</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8927</v>
+        <v>-0.6194</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.6394</v>
+        <v>-13.6268</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.72</v>
       </c>
       <c r="I107" t="n">
-        <v>1.552</v>
+        <v>1.3671</v>
       </c>
       <c r="J107" t="n">
-        <v>34.144</v>
+        <v>30.0762</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.72</v>
       </c>
       <c r="I108" t="n">
-        <v>1.552</v>
+        <v>1.3671</v>
       </c>
       <c r="J108" t="n">
-        <v>34.144</v>
+        <v>30.0762</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.47</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0638</v>
+        <v>1.0685</v>
       </c>
       <c r="J109" t="n">
-        <v>23.4036</v>
+        <v>23.507</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.06</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0509</v>
+        <v>0.1391</v>
       </c>
       <c r="J110" t="n">
-        <v>1.1198</v>
+        <v>3.0602</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1803</v>
+        <v>-0.0936</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.9666</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.71</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.3351</v>
+        <v>-0.2728</v>
       </c>
       <c r="J112" t="n">
-        <v>-6.702</v>
+        <v>-5.456</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3351</v>
+        <v>-0.2728</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.702</v>
+        <v>-5.456</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.63</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4664</v>
+        <v>-0.3498</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.327999999999999</v>
+        <v>-6.996</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.58</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5655</v>
+        <v>-0.3936</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.31</v>
+        <v>-7.872</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7533</v>
+        <v>-0.5153</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.066</v>
+        <v>-10.306</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2043</v>
+        <v>1.1517</v>
       </c>
       <c r="J117" t="n">
-        <v>24.086</v>
+        <v>23.034</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.53</v>
       </c>
       <c r="I118" t="n">
-        <v>1.184</v>
+        <v>1.1397</v>
       </c>
       <c r="J118" t="n">
-        <v>23.68</v>
+        <v>22.794</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.918</v>
+        <v>0.9827</v>
       </c>
       <c r="J119" t="n">
-        <v>18.36</v>
+        <v>19.654</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.36</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7865</v>
+        <v>0.8872</v>
       </c>
       <c r="J120" t="n">
-        <v>15.73</v>
+        <v>17.744</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.18</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3668</v>
+        <v>0.4692</v>
       </c>
       <c r="J121" t="n">
-        <v>7.336</v>
+        <v>9.384</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6549</v>
+        <v>0.8882</v>
       </c>
       <c r="J122" t="n">
-        <v>12.4431</v>
+        <v>16.8758</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.46</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.4914</v>
       </c>
       <c r="J123" t="n">
-        <v>-13.5128</v>
+        <v>-9.336600000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.41</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.7829</v>
+        <v>-0.5393</v>
       </c>
       <c r="J124" t="n">
-        <v>-14.8751</v>
+        <v>-10.2467</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.31</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.9162</v>
+        <v>-0.637</v>
       </c>
       <c r="J125" t="n">
-        <v>-17.4078</v>
+        <v>-12.103</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.3</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9291</v>
+        <v>-0.6468</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.6529</v>
+        <v>-12.2892</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.86</v>
       </c>
       <c r="I127" t="n">
-        <v>1.7456</v>
+        <v>1.5015</v>
       </c>
       <c r="J127" t="n">
-        <v>33.1664</v>
+        <v>28.5285</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.74</v>
       </c>
       <c r="I128" t="n">
-        <v>1.5321</v>
+        <v>1.3663</v>
       </c>
       <c r="J128" t="n">
-        <v>29.1099</v>
+        <v>25.9597</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.51</v>
       </c>
       <c r="I129" t="n">
-        <v>1.0548</v>
+        <v>1.1039</v>
       </c>
       <c r="J129" t="n">
-        <v>20.0412</v>
+        <v>20.9741</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.4</v>
       </c>
       <c r="I130" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.9478</v>
       </c>
       <c r="J130" t="n">
-        <v>15.523</v>
+        <v>18.0082</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.13</v>
       </c>
       <c r="I131" t="n">
-        <v>0.2097</v>
+        <v>0.3133</v>
       </c>
       <c r="J131" t="n">
-        <v>3.9843</v>
+        <v>5.9527</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.91</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0481</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.0582</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.78</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2618</v>
+        <v>-0.2169</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.7596</v>
+        <v>-4.7718</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.77</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2778</v>
+        <v>-0.2272</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.1116</v>
+        <v>-4.9984</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.48</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.7331</v>
+        <v>-0.4985</v>
       </c>
       <c r="J135" t="n">
-        <v>-16.1282</v>
+        <v>-10.967</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.47</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.746</v>
+        <v>-0.5079</v>
       </c>
       <c r="J136" t="n">
-        <v>-16.412</v>
+        <v>-11.1738</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4192</v>
+        <v>1.2923</v>
       </c>
       <c r="J137" t="n">
-        <v>31.2224</v>
+        <v>28.4306</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.63</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3427</v>
+        <v>1.246</v>
       </c>
       <c r="J138" t="n">
-        <v>29.5394</v>
+        <v>27.412</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1174</v>
+        <v>1.118</v>
       </c>
       <c r="J139" t="n">
-        <v>24.5828</v>
+        <v>24.596</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.48</v>
       </c>
       <c r="I140" t="n">
-        <v>1.0144</v>
+        <v>1.0719</v>
       </c>
       <c r="J140" t="n">
-        <v>22.3168</v>
+        <v>23.5818</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2444</v>
+        <v>0.348</v>
       </c>
       <c r="J141" t="n">
-        <v>5.3768</v>
+        <v>7.656</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4304</v>
+        <v>0.502</v>
       </c>
       <c r="J142" t="n">
-        <v>11.6208</v>
+        <v>13.554</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2988</v>
+        <v>0.3374</v>
       </c>
       <c r="J143" t="n">
-        <v>8.067600000000001</v>
+        <v>9.1098</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0171</v>
+        <v>0.0346</v>
       </c>
       <c r="J144" t="n">
-        <v>0.4617</v>
+        <v>0.9342</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.081</v>
+        <v>-0.0385</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.187</v>
+        <v>-1.0395</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4456</v>
+        <v>-0.2817</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.0312</v>
+        <v>-7.6059</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.99</v>
       </c>
       <c r="I147" t="n">
-        <v>2.0417</v>
+        <v>1.7661</v>
       </c>
       <c r="J147" t="n">
-        <v>55.1259</v>
+        <v>47.6847</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.26</v>
       </c>
       <c r="I148" t="n">
-        <v>0.727</v>
+        <v>0.7149</v>
       </c>
       <c r="J148" t="n">
-        <v>19.629</v>
+        <v>19.3023</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4025</v>
+        <v>-0.331</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.8675</v>
+        <v>-8.936999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6434</v>
+        <v>-0.5837</v>
       </c>
       <c r="J150" t="n">
-        <v>-17.3718</v>
+        <v>-15.7599</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8557</v>
+        <v>-0.8144</v>
       </c>
       <c r="J151" t="n">
-        <v>-23.1039</v>
+        <v>-21.9888</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3676</v>
+        <v>0.4251</v>
       </c>
       <c r="J152" t="n">
-        <v>10.6604</v>
+        <v>12.3279</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3382</v>
+        <v>0.3887</v>
       </c>
       <c r="J153" t="n">
-        <v>9.8078</v>
+        <v>11.2723</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2436</v>
+        <v>0.2756</v>
       </c>
       <c r="J154" t="n">
-        <v>7.0644</v>
+        <v>7.9924</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.96</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1317</v>
+        <v>-0.0678</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.8193</v>
+        <v>-1.9662</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.77</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4354</v>
+        <v>-0.274</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.6266</v>
+        <v>-7.946</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.24</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7208</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>20.9032</v>
+        <v>20.039</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.19</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5957</v>
+        <v>0.5655</v>
       </c>
       <c r="J158" t="n">
-        <v>17.2753</v>
+        <v>16.3995</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.1</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3401</v>
+        <v>0.3271</v>
       </c>
       <c r="J159" t="n">
-        <v>9.8629</v>
+        <v>9.485900000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2706</v>
+        <v>0.271</v>
       </c>
       <c r="J160" t="n">
-        <v>7.8474</v>
+        <v>7.859</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.77</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.767</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.243</v>
+        <v>-20.8887</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.96</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0092</v>
+        <v>-0.037</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.2208</v>
+        <v>-0.888</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.88</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1573</v>
+        <v>-0.1341</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.7752</v>
+        <v>-3.2184</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1747</v>
+        <v>-0.145</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.1928</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.78</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3449</v>
+        <v>-0.2345</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.2776</v>
+        <v>-5.628</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.52</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7103</v>
+        <v>-0.4793</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.0472</v>
+        <v>-11.5032</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.66</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4987</v>
+        <v>1.3247</v>
       </c>
       <c r="J167" t="n">
-        <v>35.9688</v>
+        <v>31.7928</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.32</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7993</v>
+        <v>0.8226</v>
       </c>
       <c r="J168" t="n">
-        <v>19.1832</v>
+        <v>19.7424</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.26</v>
       </c>
       <c r="I169" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6893</v>
       </c>
       <c r="J169" t="n">
-        <v>15.2064</v>
+        <v>16.5432</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.15</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3432</v>
+        <v>0.4226</v>
       </c>
       <c r="J170" t="n">
-        <v>8.236800000000001</v>
+        <v>10.1424</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3796</v>
+        <v>-0.2988</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.1104</v>
+        <v>-7.1712</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1048</v>
+        <v>1.0189</v>
       </c>
       <c r="J172" t="n">
-        <v>18.7816</v>
+        <v>17.3213</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.71</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8037</v>
+        <v>0.7713</v>
       </c>
       <c r="J173" t="n">
-        <v>13.6629</v>
+        <v>13.1121</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.6</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6667</v>
+        <v>0.6681</v>
       </c>
       <c r="J174" t="n">
-        <v>11.3339</v>
+        <v>11.3577</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.6</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6667</v>
+        <v>0.6681</v>
       </c>
       <c r="J175" t="n">
-        <v>11.3339</v>
+        <v>11.3577</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.54</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5991</v>
+        <v>0.6087</v>
       </c>
       <c r="J176" t="n">
-        <v>10.1847</v>
+        <v>10.3479</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.82</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1115</v>
+        <v>-0.1154</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.8955</v>
+        <v>-1.9618</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.7</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2973</v>
+        <v>-0.2545</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.0541</v>
+        <v>-4.3265</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.67</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.343</v>
+        <v>-0.2869</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.831</v>
+        <v>-4.8773</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.26</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.6837</v>
       </c>
       <c r="J180" t="n">
-        <v>-16.5971</v>
+        <v>-11.6229</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.19</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.0632</v>
+        <v>-0.7539</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.0744</v>
+        <v>-12.8163</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.54</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7796</v>
+        <v>0.9698</v>
       </c>
       <c r="J182" t="n">
-        <v>46.776</v>
+        <v>58.188</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.06</v>
       </c>
       <c r="I183" t="n">
-        <v>0.101</v>
+        <v>0.1481</v>
       </c>
       <c r="J183" t="n">
-        <v>6.06</v>
+        <v>8.885999999999999</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0603</v>
+        <v>0.103</v>
       </c>
       <c r="J184" t="n">
-        <v>3.618</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1835</v>
+        <v>-0.0978</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.01</v>
+        <v>-5.868</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.88</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2845</v>
+        <v>-0.1663</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.07</v>
+        <v>-9.978</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.17</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5647</v>
+        <v>0.5256</v>
       </c>
       <c r="J187" t="n">
-        <v>33.882</v>
+        <v>31.536</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3671</v>
+        <v>0.3355</v>
       </c>
       <c r="J188" t="n">
-        <v>22.026</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0444</v>
+        <v>-0.0083</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.664</v>
+        <v>-0.498</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.98</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1503</v>
+        <v>-0.1035</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.018000000000001</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2269</v>
+        <v>-0.1752</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.614</v>
+        <v>-10.512</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.43</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6733</v>
+        <v>0.8264</v>
       </c>
       <c r="J192" t="n">
-        <v>22.8922</v>
+        <v>28.0976</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4448</v>
+        <v>0.5203</v>
       </c>
       <c r="J193" t="n">
-        <v>15.1232</v>
+        <v>17.6902</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.93</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1831</v>
+        <v>-0.1028</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.2254</v>
+        <v>-3.4952</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2187</v>
+        <v>-0.1259</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.4358</v>
+        <v>-4.2806</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.61</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6374</v>
+        <v>-0.4227</v>
       </c>
       <c r="J196" t="n">
-        <v>-21.6716</v>
+        <v>-14.3718</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1828</v>
+        <v>1.1133</v>
       </c>
       <c r="J197" t="n">
-        <v>40.2152</v>
+        <v>37.8522</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.34</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.8988</v>
       </c>
       <c r="J198" t="n">
-        <v>30.8312</v>
+        <v>30.5592</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4109</v>
+        <v>0.4448</v>
       </c>
       <c r="J199" t="n">
-        <v>13.9706</v>
+        <v>15.1232</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.406</v>
+        <v>-0.3337</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.804</v>
+        <v>-11.3458</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4349</v>
+        <v>-0.3635</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.7866</v>
+        <v>-12.359</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.25</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5651</v>
+        <v>0.5275</v>
       </c>
       <c r="J202" t="n">
-        <v>11.8671</v>
+        <v>11.0775</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.9</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0839</v>
+        <v>-0.0934</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.7619</v>
+        <v>-1.9614</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.65</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.5114</v>
+        <v>-0.3458</v>
       </c>
       <c r="J204" t="n">
-        <v>-10.7394</v>
+        <v>-7.2618</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.43</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.5511</v>
       </c>
       <c r="J205" t="n">
-        <v>-16.9029</v>
+        <v>-11.5731</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.37</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8773</v>
+        <v>-0.6068</v>
       </c>
       <c r="J206" t="n">
-        <v>-18.4233</v>
+        <v>-12.7428</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.7</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.7861</v>
       </c>
       <c r="J207" t="n">
-        <v>17.9613</v>
+        <v>16.5081</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.6</v>
       </c>
       <c r="I208" t="n">
-        <v>0.746</v>
+        <v>0.6866</v>
       </c>
       <c r="J208" t="n">
-        <v>15.666</v>
+        <v>14.4186</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.38</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4619</v>
+        <v>0.463</v>
       </c>
       <c r="J209" t="n">
-        <v>9.6999</v>
+        <v>9.723000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.36</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4364</v>
+        <v>0.4414</v>
       </c>
       <c r="J210" t="n">
-        <v>9.164400000000001</v>
+        <v>9.269399999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.25</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2954</v>
+        <v>0.3162</v>
       </c>
       <c r="J211" t="n">
-        <v>6.2034</v>
+        <v>6.6402</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.4</v>
       </c>
       <c r="I212" t="n">
-        <v>1.068</v>
+        <v>1.0341</v>
       </c>
       <c r="J212" t="n">
-        <v>29.904</v>
+        <v>28.9548</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4133</v>
+        <v>0.403</v>
       </c>
       <c r="J213" t="n">
-        <v>11.5724</v>
+        <v>11.284</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.06</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1698</v>
+        <v>0.208</v>
       </c>
       <c r="J214" t="n">
-        <v>4.7544</v>
+        <v>5.824</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1698</v>
+        <v>0.208</v>
       </c>
       <c r="J215" t="n">
-        <v>4.7544</v>
+        <v>5.824</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5775</v>
+        <v>-0.5172</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.17</v>
+        <v>-14.4816</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4974</v>
+        <v>0.586</v>
       </c>
       <c r="J217" t="n">
-        <v>13.9272</v>
+        <v>16.408</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.22</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4156</v>
+        <v>0.4786</v>
       </c>
       <c r="J218" t="n">
-        <v>11.6368</v>
+        <v>13.4008</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1706</v>
+        <v>-0.099</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.7768</v>
+        <v>-2.772</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.77</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4239</v>
+        <v>-0.2676</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.8692</v>
+        <v>-7.4928</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.75</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4516</v>
+        <v>-0.2871</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.6448</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.63</v>
       </c>
       <c r="I222" t="n">
-        <v>1.5163</v>
+        <v>1.3328</v>
       </c>
       <c r="J222" t="n">
-        <v>62.1683</v>
+        <v>54.6448</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.21</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6222</v>
+        <v>0.6031</v>
       </c>
       <c r="J223" t="n">
-        <v>25.5102</v>
+        <v>24.7271</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1921</v>
+        <v>0.2348</v>
       </c>
       <c r="J224" t="n">
-        <v>7.8761</v>
+        <v>9.626799999999999</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2973</v>
+        <v>-0.2285</v>
       </c>
       <c r="J225" t="n">
-        <v>-12.1893</v>
+        <v>-9.368499999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8928</v>
+        <v>-0.8559</v>
       </c>
       <c r="J226" t="n">
-        <v>-36.6048</v>
+        <v>-35.0919</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.52</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7639</v>
+        <v>0.9502</v>
       </c>
       <c r="J227" t="n">
-        <v>31.3199</v>
+        <v>38.9582</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2338</v>
+        <v>0.2708</v>
       </c>
       <c r="J228" t="n">
-        <v>9.585800000000001</v>
+        <v>11.1028</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1184</v>
+        <v>-0.0569</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.8544</v>
+        <v>-2.3329</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2306</v>
+        <v>-0.1307</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.454599999999999</v>
+        <v>-5.3587</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3554</v>
+        <v>-0.2165</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.5714</v>
+        <v>-8.8765</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.76</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2641</v>
+        <v>-0.2242</v>
       </c>
       <c r="J232" t="n">
-        <v>-5.282</v>
+        <v>-4.484</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.7</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3579</v>
+        <v>-0.2857</v>
       </c>
       <c r="J233" t="n">
-        <v>-7.158</v>
+        <v>-5.714</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.59</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5567</v>
+        <v>-0.3865</v>
       </c>
       <c r="J234" t="n">
-        <v>-11.134</v>
+        <v>-7.73</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.58</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5726</v>
+        <v>-0.3956</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.452</v>
+        <v>-7.912</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.51</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6756</v>
+        <v>-0.4608</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.512</v>
+        <v>-9.215999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.62</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7705</v>
+        <v>0.7076</v>
       </c>
       <c r="J237" t="n">
-        <v>15.41</v>
+        <v>14.152</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.62</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7705</v>
+        <v>0.7076</v>
       </c>
       <c r="J238" t="n">
-        <v>15.41</v>
+        <v>14.152</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.53</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6671</v>
+        <v>0.617</v>
       </c>
       <c r="J239" t="n">
-        <v>13.342</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.37</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4513</v>
+        <v>0.453</v>
       </c>
       <c r="J240" t="n">
-        <v>9.026</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.11</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1016</v>
+        <v>0.1379</v>
       </c>
       <c r="J241" t="n">
-        <v>2.032</v>
+        <v>2.758</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.51</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3181</v>
+        <v>1.1985</v>
       </c>
       <c r="J242" t="n">
-        <v>44.8154</v>
+        <v>40.749</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.18</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5834</v>
+        <v>0.5474</v>
       </c>
       <c r="J243" t="n">
-        <v>19.8356</v>
+        <v>18.6116</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0432</v>
       </c>
       <c r="J244" t="n">
-        <v>0.289</v>
+        <v>1.4688</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6629</v>
+        <v>-0.6109</v>
       </c>
       <c r="J245" t="n">
-        <v>-22.5386</v>
+        <v>-20.7706</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.76</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.7396</v>
       </c>
       <c r="J246" t="n">
-        <v>-26.6492</v>
+        <v>-25.1464</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.2</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3711</v>
+        <v>0.4279</v>
       </c>
       <c r="J247" t="n">
-        <v>12.6174</v>
+        <v>14.5486</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1958</v>
+        <v>0.218</v>
       </c>
       <c r="J248" t="n">
-        <v>6.6572</v>
+        <v>7.412</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1584</v>
+        <v>0.1765</v>
       </c>
       <c r="J249" t="n">
-        <v>5.3856</v>
+        <v>6.001</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1677</v>
+        <v>-0.0919</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.7018</v>
+        <v>-3.1246</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.88</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2713</v>
+        <v>-0.1602</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.2242</v>
+        <v>-5.4468</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.37</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9686</v>
+        <v>0.9603</v>
       </c>
       <c r="J252" t="n">
-        <v>28.0894</v>
+        <v>27.8487</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.34</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9025</v>
+        <v>0.896</v>
       </c>
       <c r="J253" t="n">
-        <v>26.1725</v>
+        <v>25.984</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.16</v>
       </c>
       <c r="I254" t="n">
-        <v>0.4346</v>
+        <v>0.4686</v>
       </c>
       <c r="J254" t="n">
-        <v>12.6034</v>
+        <v>13.5894</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.11</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2841</v>
+        <v>0.3381</v>
       </c>
       <c r="J255" t="n">
-        <v>8.238899999999999</v>
+        <v>9.8049</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.85</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5347</v>
       </c>
       <c r="J256" t="n">
-        <v>-17.3507</v>
+        <v>-15.5063</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.7083</v>
       </c>
       <c r="J257" t="n">
-        <v>17.0578</v>
+        <v>20.5407</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2494</v>
+        <v>0.2698</v>
       </c>
       <c r="J258" t="n">
-        <v>7.2326</v>
+        <v>7.8242</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.92</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1884</v>
+        <v>-0.1104</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.4636</v>
+        <v>-3.2016</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.9</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.224</v>
+        <v>-0.1329</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.496</v>
+        <v>-3.8541</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.66</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5696</v>
+        <v>-0.3725</v>
       </c>
       <c r="J261" t="n">
-        <v>-16.5184</v>
+        <v>-10.8025</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.56</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7709</v>
+        <v>0.6892</v>
       </c>
       <c r="J262" t="n">
-        <v>18.5016</v>
+        <v>16.5408</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.4144</v>
+        <v>0.3644</v>
       </c>
       <c r="J263" t="n">
-        <v>9.945600000000001</v>
+        <v>8.7456</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3236</v>
+        <v>0.2936</v>
       </c>
       <c r="J264" t="n">
-        <v>7.7664</v>
+        <v>7.0464</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0704</v>
+        <v>-0.0185</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.6896</v>
+        <v>-0.444</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.95</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1884</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.5216</v>
+        <v>-2.3088</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.01</v>
       </c>
       <c r="I267" t="n">
-        <v>0.1027</v>
+        <v>0.0548</v>
       </c>
       <c r="J267" t="n">
-        <v>2.4648</v>
+        <v>1.3152</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1</v>
       </c>
       <c r="I268" t="n">
-        <v>0.068</v>
+        <v>0.0245</v>
       </c>
       <c r="J268" t="n">
-        <v>1.632</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2751</v>
+        <v>-0.1826</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.6024</v>
+        <v>-4.3824</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3424</v>
+        <v>-0.2224</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.217599999999999</v>
+        <v>-5.3376</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.67</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5309</v>
+        <v>-0.3479</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.7416</v>
+        <v>-8.349600000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6581</v>
+        <v>0.8046</v>
       </c>
       <c r="J272" t="n">
-        <v>19.0849</v>
+        <v>23.3334</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.01</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0599</v>
+        <v>0.0439</v>
       </c>
       <c r="J273" t="n">
-        <v>1.7371</v>
+        <v>1.2731</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.91</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1974</v>
+        <v>-0.1192</v>
       </c>
       <c r="J274" t="n">
-        <v>-5.7246</v>
+        <v>-3.4568</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.85</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2987</v>
+        <v>-0.1838</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.6623</v>
+        <v>-5.3302</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.65</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.3791</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.7649</v>
+        <v>-10.9939</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.5</v>
       </c>
       <c r="I277" t="n">
-        <v>1.2232</v>
+        <v>1.142</v>
       </c>
       <c r="J277" t="n">
-        <v>35.4728</v>
+        <v>33.118</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8396</v>
+        <v>0.84</v>
       </c>
       <c r="J278" t="n">
-        <v>24.3484</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5631</v>
+        <v>0.5838</v>
       </c>
       <c r="J279" t="n">
-        <v>16.3299</v>
+        <v>16.9302</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.0157</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>0.4553</v>
+        <v>2.465</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.93</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3896</v>
+        <v>-0.3134</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.2984</v>
+        <v>-9.0886</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5342</v>
+        <v>0.6481</v>
       </c>
       <c r="J282" t="n">
-        <v>11.7524</v>
+        <v>14.2582</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.74</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.3356</v>
+        <v>-0.2602</v>
       </c>
       <c r="J283" t="n">
-        <v>-7.3832</v>
+        <v>-5.7244</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.4328</v>
+        <v>-0.306</v>
       </c>
       <c r="J284" t="n">
-        <v>-9.521599999999999</v>
+        <v>-6.732</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.48</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.7373</v>
+        <v>-0.5011</v>
       </c>
       <c r="J285" t="n">
-        <v>-16.2206</v>
+        <v>-11.0242</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.36</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.6132</v>
       </c>
       <c r="J286" t="n">
-        <v>-19.4832</v>
+        <v>-13.4904</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1832</v>
+        <v>1.1336</v>
       </c>
       <c r="J287" t="n">
-        <v>26.0304</v>
+        <v>24.9392</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1423</v>
+        <v>1.1092</v>
       </c>
       <c r="J288" t="n">
-        <v>25.1306</v>
+        <v>24.4024</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.45</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0371</v>
+        <v>1.0471</v>
       </c>
       <c r="J289" t="n">
-        <v>22.8162</v>
+        <v>23.0362</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.31</v>
       </c>
       <c r="I290" t="n">
-        <v>0.6913</v>
+        <v>0.7852</v>
       </c>
       <c r="J290" t="n">
-        <v>15.2086</v>
+        <v>17.2744</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.0041</v>
+        <v>0.0806</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.0902</v>
+        <v>1.7732</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.53</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2937</v>
+        <v>1.1861</v>
       </c>
       <c r="J292" t="n">
-        <v>36.2236</v>
+        <v>33.2108</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1736</v>
+        <v>1.1087</v>
       </c>
       <c r="J293" t="n">
-        <v>32.8608</v>
+        <v>31.0436</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.07</v>
       </c>
       <c r="I294" t="n">
-        <v>0.158</v>
+        <v>0.2207</v>
       </c>
       <c r="J294" t="n">
-        <v>4.424</v>
+        <v>6.1796</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.98</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2149</v>
+        <v>-0.1386</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.0172</v>
+        <v>-3.8808</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6512</v>
+        <v>-0.5908</v>
       </c>
       <c r="J296" t="n">
-        <v>-18.2336</v>
+        <v>-16.5424</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.3</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5534</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J297" t="n">
-        <v>15.4952</v>
+        <v>18.4464</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4173</v>
+        <v>0.4742</v>
       </c>
       <c r="J298" t="n">
-        <v>11.6844</v>
+        <v>13.2776</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3424</v>
+        <v>-0.2176</v>
       </c>
       <c r="J299" t="n">
-        <v>-9.587199999999999</v>
+        <v>-6.0928</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.7</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5007</v>
+        <v>-0.3249</v>
       </c>
       <c r="J300" t="n">
-        <v>-14.0196</v>
+        <v>-9.097200000000001</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.52</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7282</v>
+        <v>-0.492</v>
       </c>
       <c r="J301" t="n">
-        <v>-20.3896</v>
+        <v>-13.776</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.5</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2765</v>
+        <v>1.1714</v>
       </c>
       <c r="J302" t="n">
-        <v>45.954</v>
+        <v>42.1704</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.36</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9659</v>
       </c>
       <c r="J303" t="n">
-        <v>35.4744</v>
+        <v>34.7724</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.02</v>
       </c>
       <c r="I304" t="n">
-        <v>0.0271</v>
+        <v>0.0741</v>
       </c>
       <c r="J304" t="n">
-        <v>0.9756</v>
+        <v>2.6676</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.5493</v>
+        <v>-0.4883</v>
       </c>
       <c r="J305" t="n">
-        <v>-19.7748</v>
+        <v>-17.5788</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.8646</v>
+        <v>-0.8256</v>
       </c>
       <c r="J306" t="n">
-        <v>-31.1256</v>
+        <v>-29.7216</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.22</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4011</v>
+        <v>0.4651</v>
       </c>
       <c r="J307" t="n">
-        <v>14.4396</v>
+        <v>16.7436</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.06</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1405</v>
+        <v>0.1557</v>
       </c>
       <c r="J308" t="n">
-        <v>5.058</v>
+        <v>5.6052</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1196</v>
+        <v>0.1337</v>
       </c>
       <c r="J309" t="n">
-        <v>4.3056</v>
+        <v>4.8132</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.99</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.0568</v>
+        <v>-0.0232</v>
       </c>
       <c r="J310" t="n">
-        <v>-2.0448</v>
+        <v>-0.8352000000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.84</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3323</v>
+        <v>-0.202</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.9628</v>
+        <v>-7.272</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.31</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8542</v>
       </c>
       <c r="J312" t="n">
-        <v>26.265</v>
+        <v>25.626</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5054</v>
+        <v>0.4835</v>
       </c>
       <c r="J313" t="n">
-        <v>15.162</v>
+        <v>14.505</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2103</v>
+        <v>0.2399</v>
       </c>
       <c r="J314" t="n">
-        <v>6.309</v>
+        <v>7.197</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.01</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.0154</v>
+        <v>0.0338</v>
       </c>
       <c r="J315" t="n">
-        <v>-0.462</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4105</v>
+        <v>-0.3458</v>
       </c>
       <c r="J316" t="n">
-        <v>-12.315</v>
+        <v>-10.374</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.32</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5556</v>
+        <v>0.6633</v>
       </c>
       <c r="J317" t="n">
-        <v>16.668</v>
+        <v>19.899</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2215</v>
+        <v>0.233</v>
       </c>
       <c r="J318" t="n">
-        <v>6.645</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.89</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2357</v>
+        <v>-0.1421</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.071</v>
+        <v>-4.263</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.78</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4056</v>
+        <v>-0.2556</v>
       </c>
       <c r="J320" t="n">
-        <v>-12.168</v>
+        <v>-7.668</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.78</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4056</v>
+        <v>-0.2556</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.168</v>
+        <v>-7.668</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.5</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1303</v>
+        <v>1.1057</v>
       </c>
       <c r="J322" t="n">
-        <v>25.9969</v>
+        <v>25.4311</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9788</v>
+        <v>1.016</v>
       </c>
       <c r="J323" t="n">
-        <v>22.5124</v>
+        <v>23.368</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.42</v>
       </c>
       <c r="I324" t="n">
-        <v>0.9556</v>
+        <v>1.0006</v>
       </c>
       <c r="J324" t="n">
-        <v>21.9788</v>
+        <v>23.0138</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.37</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8213</v>
+        <v>0.9105</v>
       </c>
       <c r="J325" t="n">
-        <v>18.8899</v>
+        <v>20.9415</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.22</v>
       </c>
       <c r="I326" t="n">
-        <v>0.4685</v>
+        <v>0.5715</v>
       </c>
       <c r="J326" t="n">
-        <v>10.7755</v>
+        <v>13.1445</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.02</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1751</v>
+        <v>0.1518</v>
       </c>
       <c r="J327" t="n">
-        <v>4.0273</v>
+        <v>3.4914</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2505</v>
+        <v>-0.1998</v>
       </c>
       <c r="J328" t="n">
-        <v>-5.7615</v>
+        <v>-4.5954</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.73</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4006</v>
+        <v>-0.2757</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.213800000000001</v>
+        <v>-6.3411</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.7</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4497</v>
+        <v>-0.3037</v>
       </c>
       <c r="J330" t="n">
-        <v>-10.3431</v>
+        <v>-6.9851</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.5</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7247</v>
+        <v>-0.4907</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.6681</v>
+        <v>-11.2861</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3190/event_3190_evp_summary.xlsx
+++ b/database/event/3190/event_3190_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6483</v>
+        <v>6.6606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.614</v>
+        <v>0.6152</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3634</v>
+        <v>2.4078</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6483</v>
+        <v>6.6606</v>
       </c>
       <c r="F2" t="n">
-        <v>3.939</v>
+        <v>3.8655</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7093</v>
+        <v>2.7951</v>
       </c>
       <c r="H2" t="n">
-        <v>8.392099999999999</v>
+        <v>7.8594</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3635</v>
+        <v>4.244</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7093</v>
+        <v>2.7951</v>
       </c>
       <c r="K2" t="n">
         <v>160</v>
@@ -529,7 +529,7 @@
         <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>7.0728</v>
+        <v>7.039099999999999</v>
       </c>
       <c r="N2" t="n">
         <v>291</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3227</v>
+        <v>4.2263</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3992</v>
+        <v>0.3903</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3135</v>
+        <v>1.2997</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3227</v>
+        <v>4.2263</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1822</v>
+        <v>4.0733</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1405</v>
+        <v>0.153</v>
       </c>
       <c r="H3" t="n">
-        <v>9.2491</v>
+        <v>8.545199999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8091</v>
+        <v>4.6144</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1405</v>
+        <v>0.153</v>
       </c>
       <c r="K3" t="n">
         <v>211</v>
@@ -575,7 +575,7 @@
         <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9496</v>
+        <v>4.767399999999999</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0533</v>
+        <v>3.9923</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3744</v>
+        <v>0.3687</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1918</v>
+        <v>1.1932</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0533</v>
+        <v>3.9923</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5716</v>
+        <v>3.4823</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4817</v>
+        <v>0.51</v>
       </c>
       <c r="H4" t="n">
-        <v>7.0977</v>
+        <v>6.5954</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6905</v>
+        <v>3.5614</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4817</v>
+        <v>0.51</v>
       </c>
       <c r="K4" t="n">
         <v>194</v>
@@ -621,7 +621,7 @@
         <v>81</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1722</v>
+        <v>4.0714</v>
       </c>
       <c r="N4" t="n">
         <v>275</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9948</v>
+        <v>3.9646</v>
       </c>
       <c r="C5" t="n">
-        <v>0.369</v>
+        <v>0.3662</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1654</v>
+        <v>1.1806</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9948</v>
+        <v>3.9646</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4534</v>
+        <v>3.3679</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5414</v>
+        <v>0.5967</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6813</v>
+        <v>6.2179</v>
       </c>
       <c r="I5" t="n">
-        <v>3.474</v>
+        <v>3.3576</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5414</v>
+        <v>0.5967</v>
       </c>
       <c r="K5" t="n">
         <v>194</v>
@@ -667,7 +667,7 @@
         <v>81</v>
       </c>
       <c r="M5" t="n">
-        <v>4.015400000000001</v>
+        <v>3.9543</v>
       </c>
       <c r="N5" t="n">
         <v>275</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8566</v>
+        <v>3.9249</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3562</v>
+        <v>0.3625</v>
       </c>
       <c r="D6" t="n">
-        <v>1.103</v>
+        <v>1.1625</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8566</v>
+        <v>3.9249</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3873</v>
+        <v>2.3194</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4693</v>
+        <v>1.6055</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9249</v>
+        <v>2.7584</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5208</v>
+        <v>1.4895</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4693</v>
+        <v>1.6055</v>
       </c>
       <c r="K6" t="n">
         <v>160</v>
@@ -713,7 +713,7 @@
         <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9901</v>
+        <v>3.095</v>
       </c>
       <c r="N6" t="n">
         <v>291</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7473</v>
+        <v>3.7336</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3461</v>
+        <v>0.3448</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0537</v>
+        <v>1.0754</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7473</v>
+        <v>3.7336</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7247</v>
+        <v>3.0705</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0226</v>
+        <v>0.6631</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1138</v>
+        <v>5.2365</v>
       </c>
       <c r="I7" t="n">
-        <v>2.139</v>
+        <v>2.8277</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0226</v>
+        <v>0.6631</v>
       </c>
       <c r="K7" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="L7" t="n">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1616</v>
+        <v>3.4908</v>
       </c>
       <c r="N7" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7399</v>
+        <v>3.7137</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3454</v>
+        <v>0.343</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0504</v>
+        <v>1.0663</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7399</v>
+        <v>3.7137</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1401</v>
+        <v>2.6392</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5998</v>
+        <v>1.0745</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5775</v>
+        <v>3.8134</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>2.0592</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5998</v>
+        <v>1.0745</v>
       </c>
       <c r="K8" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4998</v>
+        <v>3.1337</v>
       </c>
       <c r="N8" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.536</v>
+        <v>3.5434</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3266</v>
+        <v>0.3273</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9583</v>
+        <v>0.9888</v>
       </c>
       <c r="E9" t="n">
-        <v>3.536</v>
+        <v>3.5434</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3074</v>
+        <v>0.5111</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2286</v>
+        <v>3.0323</v>
       </c>
       <c r="H9" t="n">
-        <v>6.167</v>
+        <v>0.5111</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2066</v>
+        <v>0.276</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2286</v>
+        <v>3.0323</v>
       </c>
       <c r="K9" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="L9" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4352</v>
+        <v>3.3083</v>
       </c>
       <c r="N9" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5145</v>
+        <v>3.472</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3246</v>
+        <v>0.3207</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9486</v>
+        <v>0.9563</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5145</v>
+        <v>3.472</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5602</v>
+        <v>3.2428</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9543</v>
+        <v>0.2292</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5602</v>
+        <v>5.8049</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2913</v>
+        <v>3.1346</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9543</v>
+        <v>0.2292</v>
       </c>
       <c r="K10" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="L10" t="n">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2456</v>
+        <v>3.3638</v>
       </c>
       <c r="N10" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1178</v>
+        <v>3.0367</v>
       </c>
       <c r="C11" t="n">
-        <v>0.288</v>
+        <v>0.2805</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7695</v>
+        <v>0.7582</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1178</v>
+        <v>3.0367</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7864</v>
+        <v>2.6618</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3314</v>
+        <v>0.3749</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3312</v>
+        <v>3.8882</v>
       </c>
       <c r="I11" t="n">
-        <v>2.252</v>
+        <v>2.0996</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3314</v>
+        <v>0.3749</v>
       </c>
       <c r="K11" t="n">
         <v>211</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5834</v>
+        <v>2.4745</v>
       </c>
       <c r="N11" t="n">
         <v>264</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.817</v>
+        <v>2.7132</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2602</v>
+        <v>0.2506</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6337</v>
+        <v>0.6109</v>
       </c>
       <c r="E12" t="n">
-        <v>2.817</v>
+        <v>2.7132</v>
       </c>
       <c r="F12" t="n">
-        <v>2.832</v>
+        <v>2.7321</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.015</v>
+        <v>-0.0189</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4918</v>
+        <v>4.1199</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3356</v>
+        <v>2.2247</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.015</v>
+        <v>-0.0189</v>
       </c>
       <c r="K12" t="n">
         <v>194</v>
@@ -989,7 +989,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3206</v>
+        <v>2.2058</v>
       </c>
       <c r="N12" t="n">
         <v>275</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7118</v>
+        <v>2.6558</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2505</v>
+        <v>0.2453</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5848</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7118</v>
+        <v>2.6558</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7854</v>
+        <v>2.7058</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0736</v>
+        <v>-0.05</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3277</v>
+        <v>4.0332</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2502</v>
+        <v>2.1779</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0736</v>
+        <v>-0.05</v>
       </c>
       <c r="K13" t="n">
         <v>132</v>
@@ -1035,7 +1035,7 @@
         <v>103</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1766</v>
+        <v>2.1279</v>
       </c>
       <c r="N13" t="n">
         <v>235</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5887</v>
+        <v>2.5133</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2391</v>
+        <v>0.2321</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5199</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5887</v>
+        <v>2.5133</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2138</v>
+        <v>3.1463</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6251</v>
+        <v>-0.633</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8372</v>
+        <v>5.4868</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0351</v>
+        <v>2.9628</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6251</v>
+        <v>-0.633</v>
       </c>
       <c r="K14" t="n">
         <v>211</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>2.41</v>
+        <v>2.3298</v>
       </c>
       <c r="N14" t="n">
         <v>264</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5728</v>
+        <v>2.5061</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2376</v>
+        <v>0.2315</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5235</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5728</v>
+        <v>2.5061</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5728</v>
+        <v>3.5396</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-1.0335</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5728</v>
+        <v>6.7844</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5728</v>
+        <v>3.6635</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-1.0335</v>
       </c>
       <c r="K15" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5728</v>
+        <v>2.63</v>
       </c>
       <c r="N15" t="n">
-        <v>165</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.524</v>
+        <v>2.3627</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2331</v>
+        <v>0.2182</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5014</v>
+        <v>0.4513</v>
       </c>
       <c r="E16" t="n">
-        <v>2.524</v>
+        <v>2.3627</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5999</v>
+        <v>2.3627</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0759</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>7.1976</v>
+        <v>2.4462</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7424</v>
+        <v>2.4462</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0759</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L16" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6665</v>
+        <v>2.4462</v>
       </c>
       <c r="N16" t="n">
-        <v>235</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0743</v>
+        <v>2.0221</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1916</v>
+        <v>0.1868</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2984</v>
+        <v>0.2963</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0743</v>
+        <v>2.0221</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0743</v>
+        <v>2.0221</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0743</v>
+        <v>2.0221</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0743</v>
+        <v>2.0221</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0743</v>
+        <v>2.0221</v>
       </c>
       <c r="N17" t="n">
         <v>175</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0462</v>
+        <v>1.9836</v>
       </c>
       <c r="C18" t="n">
-        <v>0.189</v>
+        <v>0.1832</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2857</v>
+        <v>0.2788</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0462</v>
+        <v>1.9836</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0462</v>
+        <v>1.9836</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0462</v>
+        <v>1.9836</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0462</v>
+        <v>1.9836</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0462</v>
+        <v>1.9836</v>
       </c>
       <c r="N18" t="n">
         <v>165</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9729</v>
+        <v>1.8009</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1822</v>
+        <v>0.1663</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2527</v>
+        <v>0.1956</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9729</v>
+        <v>1.8009</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9729</v>
+        <v>1.8009</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9729</v>
+        <v>1.8009</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9729</v>
+        <v>1.8009</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9729</v>
+        <v>1.8009</v>
       </c>
       <c r="N19" t="n">
         <v>241</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8674</v>
+        <v>1.7923</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1725</v>
+        <v>0.1655</v>
       </c>
       <c r="D20" t="n">
-        <v>0.205</v>
+        <v>0.1917</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8674</v>
+        <v>1.7923</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8674</v>
+        <v>1.7923</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8674</v>
+        <v>1.7923</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8674</v>
+        <v>1.7923</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8674</v>
+        <v>1.7923</v>
       </c>
       <c r="N20" t="n">
         <v>241</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7051</v>
+        <v>1.6408</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1575</v>
+        <v>0.1515</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1318</v>
+        <v>0.1227</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7051</v>
+        <v>1.6408</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3341</v>
+        <v>1.6408</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.629</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7377</v>
+        <v>1.6408</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4235</v>
+        <v>1.6408</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.629</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="L21" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7945</v>
+        <v>1.6408</v>
       </c>
       <c r="N21" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6891</v>
+        <v>1.6034</v>
       </c>
       <c r="C22" t="n">
-        <v>0.156</v>
+        <v>0.1481</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1245</v>
+        <v>0.1057</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6891</v>
+        <v>1.6034</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6891</v>
+        <v>2.269</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.6656</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6891</v>
+        <v>2.5922</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6891</v>
+        <v>1.3998</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.6656</v>
       </c>
       <c r="K22" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6891</v>
+        <v>0.7342</v>
       </c>
       <c r="N22" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.378</v>
+        <v>1.3465</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1273</v>
+        <v>0.1244</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0159</v>
+        <v>-0.0112</v>
       </c>
       <c r="E23" t="n">
-        <v>1.378</v>
+        <v>1.3465</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1928</v>
+        <v>2.0769</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8148</v>
+        <v>-0.7304</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2396</v>
+        <v>2.0769</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1645</v>
+        <v>1.1215</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8148</v>
+        <v>-0.7304</v>
       </c>
       <c r="K23" t="n">
         <v>132</v>
@@ -1495,7 +1495,7 @@
         <v>103</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3497000000000001</v>
+        <v>0.3910999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>235</v>
@@ -1504,139 +1504,139 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COLDYY1</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3552</v>
+        <v>1.2267</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1252</v>
+        <v>0.1133</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0262</v>
+        <v>-0.0658</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3552</v>
+        <v>1.2267</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3552</v>
+        <v>0.3085</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.9182</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3552</v>
+        <v>0.3085</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3552</v>
+        <v>0.1666</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.9182</v>
       </c>
       <c r="K24" t="n">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3552</v>
+        <v>1.0848</v>
       </c>
       <c r="N24" t="n">
-        <v>182</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2175</v>
+        <v>1.2011</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1124</v>
+        <v>0.1109</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0774</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2175</v>
+        <v>1.2011</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3535</v>
+        <v>1.2011</v>
       </c>
       <c r="G25" t="n">
-        <v>0.864</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3535</v>
+        <v>1.2011</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1838</v>
+        <v>1.2011</v>
       </c>
       <c r="J25" t="n">
-        <v>0.864</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="L25" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0478</v>
+        <v>1.2011</v>
       </c>
       <c r="N25" t="n">
-        <v>235</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>COLDYY1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.208</v>
+        <v>1.1196</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1116</v>
+        <v>0.1034</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0927</v>
+        <v>-0.1145</v>
       </c>
       <c r="E26" t="n">
-        <v>1.208</v>
+        <v>1.1196</v>
       </c>
       <c r="F26" t="n">
-        <v>1.208</v>
+        <v>1.1196</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.208</v>
+        <v>1.1196</v>
       </c>
       <c r="I26" t="n">
-        <v>1.208</v>
+        <v>1.1196</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.208</v>
+        <v>1.1196</v>
       </c>
       <c r="N26" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.106</v>
+        <v>1.0148</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1021</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1387</v>
+        <v>-0.1622</v>
       </c>
       <c r="E27" t="n">
-        <v>1.106</v>
+        <v>1.0148</v>
       </c>
       <c r="F27" t="n">
-        <v>1.106</v>
+        <v>1.0148</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.106</v>
+        <v>1.0148</v>
       </c>
       <c r="I27" t="n">
-        <v>1.106</v>
+        <v>1.0148</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.106</v>
+        <v>1.0148</v>
       </c>
       <c r="N27" t="n">
         <v>182</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0842</v>
+        <v>1.0086</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1001</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1486</v>
+        <v>-0.1651</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0842</v>
+        <v>1.0086</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0842</v>
+        <v>1.0086</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0842</v>
+        <v>1.0086</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0842</v>
+        <v>1.0086</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0842</v>
+        <v>1.0086</v>
       </c>
       <c r="N28" t="n">
         <v>241</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0067</v>
+        <v>0.9634</v>
       </c>
       <c r="C29" t="n">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1835</v>
+        <v>-0.1856</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0067</v>
+        <v>0.9634</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0067</v>
+        <v>0.9634</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0067</v>
+        <v>0.9634</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0067</v>
+        <v>0.9634</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0067</v>
+        <v>0.9634</v>
       </c>
       <c r="N29" t="n">
         <v>175</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5376</v>
+        <v>0.5944</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0497</v>
+        <v>0.0549</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3953</v>
+        <v>-0.3536</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5376</v>
+        <v>0.5944</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1004</v>
+        <v>0.1261</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4372</v>
+        <v>0.4683</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1004</v>
+        <v>0.1261</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0522</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4372</v>
+        <v>0.4683</v>
       </c>
       <c r="K30" t="n">
         <v>160</v>
@@ -1817,7 +1817,7 @@
         <v>131</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4894</v>
+        <v>0.5364</v>
       </c>
       <c r="N30" t="n">
         <v>291</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3813</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0352</v>
+        <v>0.0514</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4659</v>
+        <v>-0.3706</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3813</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3813</v>
+        <v>-1.2019</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.7588</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3813</v>
+        <v>-1.2019</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3813</v>
+        <v>-0.649</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.7588</v>
       </c>
       <c r="K31" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3813</v>
+        <v>1.1098</v>
       </c>
       <c r="N31" t="n">
-        <v>165</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2771</v>
+        <v>0.3833</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0256</v>
+        <v>0.0354</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5129</v>
+        <v>-0.4497</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2771</v>
+        <v>0.3833</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.3438</v>
+        <v>0.3833</v>
       </c>
       <c r="G32" t="n">
-        <v>1.6209</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.3438</v>
+        <v>0.3833</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6987</v>
+        <v>0.3833</v>
       </c>
       <c r="J32" t="n">
-        <v>1.6209</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L32" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9222</v>
+        <v>0.3833</v>
       </c>
       <c r="N32" t="n">
-        <v>235</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0859</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5992</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0859</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0859</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0859</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0859</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0859</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>165</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0369</v>
+        <v>0.0113</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0034</v>
+        <v>0.001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6214</v>
+        <v>-0.6191</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0369</v>
+        <v>0.0113</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0369</v>
+        <v>0.0113</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0369</v>
+        <v>0.0113</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0369</v>
+        <v>0.0113</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0369</v>
+        <v>0.0113</v>
       </c>
       <c r="N34" t="n">
         <v>175</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0056</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0005</v>
+        <v>-0.0009</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6355</v>
+        <v>-0.6287</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0056</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3437</v>
+        <v>0.3463</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3381</v>
+        <v>-0.3562</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3437</v>
+        <v>0.3463</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1787</v>
+        <v>0.187</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3381</v>
+        <v>-0.3562</v>
       </c>
       <c r="K35" t="n">
         <v>194</v>
@@ -2047,7 +2047,7 @@
         <v>81</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1594</v>
+        <v>-0.1692</v>
       </c>
       <c r="N35" t="n">
         <v>275</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4245</v>
+        <v>-0.4347</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0392</v>
+        <v>-0.0401</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8297</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4245</v>
+        <v>-0.4347</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4245</v>
+        <v>-0.4347</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4245</v>
+        <v>-0.4347</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4245</v>
+        <v>-0.4347</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4245</v>
+        <v>-0.4347</v>
       </c>
       <c r="N36" t="n">
         <v>241</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7986</v>
+        <v>-0.8294</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0738</v>
+        <v>-0.0766</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-1.0018</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7986</v>
+        <v>-0.8294</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7986</v>
+        <v>-0.8294</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7986</v>
+        <v>-0.8294</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7986</v>
+        <v>-0.8294</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7986</v>
+        <v>-0.8294</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.862</v>
+        <v>-0.9462</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0796</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0272</v>
+        <v>-1.0549</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.862</v>
+        <v>-0.9462</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.862</v>
+        <v>-0.9462</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.862</v>
+        <v>-0.9462</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.862</v>
+        <v>-0.9462</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.862</v>
+        <v>-0.9462</v>
       </c>
       <c r="N38" t="n">
         <v>182</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8346</v>
+        <v>-1.8529</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1694</v>
+        <v>-0.1711</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4662</v>
+        <v>-1.4677</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8346</v>
+        <v>-1.8529</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8346</v>
+        <v>-1.8529</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8346</v>
+        <v>-1.8529</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8346</v>
+        <v>-1.8529</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8346</v>
+        <v>-1.8529</v>
       </c>
       <c r="N39" t="n">
         <v>241</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0821</v>
+        <v>-2.0441</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1923</v>
+        <v>-0.1888</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.578</v>
+        <v>-1.5547</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0821</v>
+        <v>-2.0441</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0821</v>
+        <v>-2.0441</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0821</v>
+        <v>-2.0441</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0821</v>
+        <v>-2.0441</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0821</v>
+        <v>-2.0441</v>
       </c>
       <c r="N40" t="n">
         <v>182</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2396</v>
+        <v>-2.295</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2068</v>
+        <v>-0.212</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6491</v>
+        <v>-1.6689</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2396</v>
+        <v>-2.295</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2396</v>
+        <v>-2.295</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2396</v>
+        <v>-2.295</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2396</v>
+        <v>-2.295</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2396</v>
+        <v>-2.295</v>
       </c>
       <c r="N41" t="n">
         <v>182</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3305</v>
+        <v>0.3187</v>
       </c>
       <c r="J2" t="n">
-        <v>7.932</v>
+        <v>7.6488</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.96</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.042</v>
+        <v>-0.0562</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.008</v>
+        <v>-1.3488</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1378</v>
+        <v>-0.1553</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.3072</v>
+        <v>-3.7272</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3142</v>
+        <v>-0.3304</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.5408</v>
+        <v>-7.9296</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5191</v>
+        <v>-0.5254</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.4584</v>
+        <v>-12.6096</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0864</v>
+        <v>1.064</v>
       </c>
       <c r="J7" t="n">
-        <v>26.0736</v>
+        <v>25.536</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0478</v>
+        <v>1.0084</v>
       </c>
       <c r="J8" t="n">
-        <v>25.1472</v>
+        <v>24.2016</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9079</v>
+        <v>0.8572</v>
       </c>
       <c r="J9" t="n">
-        <v>21.7896</v>
+        <v>20.5728</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4199</v>
+        <v>0.4218</v>
       </c>
       <c r="J10" t="n">
-        <v>10.0776</v>
+        <v>10.1232</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.201</v>
+        <v>-0.1848</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.824</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7865</v>
+        <v>0.745</v>
       </c>
       <c r="J12" t="n">
-        <v>20.449</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1378</v>
+        <v>-0.1525</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.5828</v>
+        <v>-3.965</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1485</v>
+        <v>-0.1634</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.861</v>
+        <v>-4.2484</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2606</v>
+        <v>-0.2754</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.7756</v>
+        <v>-7.1604</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2898</v>
+        <v>-0.304</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.5348</v>
+        <v>-7.904</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2888</v>
+        <v>1.3503</v>
       </c>
       <c r="J17" t="n">
-        <v>33.5088</v>
+        <v>35.1078</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.708</v>
+        <v>0.6761</v>
       </c>
       <c r="J18" t="n">
-        <v>18.408</v>
+        <v>17.5786</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.364</v>
+        <v>0.3654</v>
       </c>
       <c r="J19" t="n">
-        <v>9.464</v>
+        <v>9.500400000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1262</v>
+        <v>0.1426</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2812</v>
+        <v>3.7076</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5898</v>
+        <v>-0.5505</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.3348</v>
+        <v>-14.313</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.33</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6605</v>
+        <v>0.6381</v>
       </c>
       <c r="J22" t="n">
-        <v>19.815</v>
+        <v>19.143</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.11</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2612</v>
+        <v>0.268</v>
       </c>
       <c r="J23" t="n">
-        <v>7.836</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.97</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0521</v>
+        <v>-0.0598</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.563</v>
+        <v>-1.794</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0654</v>
+        <v>-0.0742</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.962</v>
+        <v>-2.226</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.74</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3005</v>
+        <v>-0.3124</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.015000000000001</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.959</v>
+        <v>0.8993</v>
       </c>
       <c r="J27" t="n">
-        <v>28.77</v>
+        <v>26.979</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.917</v>
+        <v>0.8598</v>
       </c>
       <c r="J28" t="n">
-        <v>27.51</v>
+        <v>25.794</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.14</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4173</v>
+        <v>0.4141</v>
       </c>
       <c r="J29" t="n">
-        <v>12.519</v>
+        <v>12.423</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.08</v>
       </c>
       <c r="I30" t="n">
-        <v>0.252</v>
+        <v>0.2616</v>
       </c>
       <c r="J30" t="n">
-        <v>7.56</v>
+        <v>7.848</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3666</v>
+        <v>-0.3478</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.998</v>
+        <v>-10.434</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.4</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7548</v>
+        <v>0.7269</v>
       </c>
       <c r="J32" t="n">
-        <v>27.1728</v>
+        <v>26.1684</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3614</v>
+        <v>0.3662</v>
       </c>
       <c r="J33" t="n">
-        <v>13.0104</v>
+        <v>13.1832</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1908</v>
+        <v>0.2023</v>
       </c>
       <c r="J34" t="n">
-        <v>6.8688</v>
+        <v>7.2828</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0584</v>
+        <v>-0.0646</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.1024</v>
+        <v>-2.3256</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2484</v>
+        <v>-0.2597</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.942399999999999</v>
+        <v>-9.3492</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.35</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9744</v>
+        <v>0.9042</v>
       </c>
       <c r="J37" t="n">
-        <v>35.0784</v>
+        <v>32.5512</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3115</v>
+        <v>0.3094</v>
       </c>
       <c r="J38" t="n">
-        <v>11.214</v>
+        <v>11.1384</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2361</v>
+        <v>-0.2353</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.499599999999999</v>
+        <v>-8.470800000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.9</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3563</v>
+        <v>-0.3472</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.8268</v>
+        <v>-12.4992</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4962</v>
+        <v>-0.4743</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.8632</v>
+        <v>-17.0748</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3205</v>
+        <v>0.3211</v>
       </c>
       <c r="J42" t="n">
-        <v>9.615</v>
+        <v>9.632999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2186</v>
+        <v>0.2223</v>
       </c>
       <c r="J43" t="n">
-        <v>6.558</v>
+        <v>6.669</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0321</v>
+        <v>-0.0398</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.963</v>
+        <v>-1.194</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1922</v>
+        <v>-0.2071</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.766</v>
+        <v>-6.213</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3206</v>
+        <v>-0.3337</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.618</v>
+        <v>-10.011</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7002</v>
+        <v>0.7726</v>
       </c>
       <c r="J47" t="n">
-        <v>21.006</v>
+        <v>23.178</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.23</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5191</v>
+        <v>0.5732</v>
       </c>
       <c r="J48" t="n">
-        <v>15.573</v>
+        <v>17.196</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4166</v>
+        <v>0.4573</v>
       </c>
       <c r="J49" t="n">
-        <v>12.498</v>
+        <v>13.719</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2323</v>
+        <v>-0.2246</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.969</v>
+        <v>-6.738</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2323</v>
+        <v>-0.2246</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.969</v>
+        <v>-6.738</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4968</v>
+        <v>0.5676</v>
       </c>
       <c r="J52" t="n">
-        <v>13.4136</v>
+        <v>15.3252</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.32</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3849</v>
+        <v>0.4316</v>
       </c>
       <c r="J53" t="n">
-        <v>10.3923</v>
+        <v>11.6532</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.25</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3348</v>
+        <v>0.3558</v>
       </c>
       <c r="J54" t="n">
-        <v>9.0396</v>
+        <v>9.6066</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.04</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0585</v>
+        <v>0.0745</v>
       </c>
       <c r="J55" t="n">
-        <v>1.5795</v>
+        <v>2.0115</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0847</v>
+        <v>-0.0892</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.2869</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3235</v>
+        <v>0.3263</v>
       </c>
       <c r="J57" t="n">
-        <v>8.734500000000001</v>
+        <v>8.8101</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.97</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0445</v>
+        <v>-0.0541</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.2015</v>
+        <v>-1.4607</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0704</v>
+        <v>-0.0819</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.9008</v>
+        <v>-2.2113</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2308</v>
+        <v>-0.246</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.2316</v>
+        <v>-6.642</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2704</v>
+        <v>-0.285</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.3008</v>
+        <v>-7.695</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.84</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.174</v>
+        <v>-0.1932</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.176</v>
+        <v>-4.6368</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2044</v>
+        <v>-0.2236</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.9056</v>
+        <v>-5.3664</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2237</v>
+        <v>-0.2427</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.3688</v>
+        <v>-5.8248</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.79</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2237</v>
+        <v>-0.2427</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.3688</v>
+        <v>-5.8248</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3177</v>
+        <v>-0.3349</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.6248</v>
+        <v>-8.037599999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.79</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2063</v>
+        <v>1.3196</v>
       </c>
       <c r="J67" t="n">
-        <v>28.9512</v>
+        <v>31.6704</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5429</v>
+        <v>0.6044</v>
       </c>
       <c r="J68" t="n">
-        <v>13.0296</v>
+        <v>14.5056</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3855</v>
+        <v>0.4216</v>
       </c>
       <c r="J69" t="n">
-        <v>9.252000000000001</v>
+        <v>10.1184</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3542</v>
+        <v>0.3745</v>
       </c>
       <c r="J70" t="n">
-        <v>8.5008</v>
+        <v>8.988</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0669</v>
+        <v>0.0919</v>
       </c>
       <c r="J71" t="n">
-        <v>1.6056</v>
+        <v>2.2056</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7921</v>
+        <v>0.8647</v>
       </c>
       <c r="J72" t="n">
-        <v>23.763</v>
+        <v>25.941</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5916</v>
+        <v>0.6469</v>
       </c>
       <c r="J73" t="n">
-        <v>17.748</v>
+        <v>19.407</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4902</v>
+        <v>-0.4701</v>
       </c>
       <c r="J74" t="n">
-        <v>-14.706</v>
+        <v>-14.103</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.79</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6489</v>
+        <v>-0.6117</v>
       </c>
       <c r="J75" t="n">
-        <v>-19.467</v>
+        <v>-18.351</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.73</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8012</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-24.036</v>
+        <v>-22.365</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5342</v>
+        <v>0.5997</v>
       </c>
       <c r="J77" t="n">
-        <v>16.026</v>
+        <v>17.991</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.32</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4956</v>
+        <v>0.5556</v>
       </c>
       <c r="J78" t="n">
-        <v>14.868</v>
+        <v>16.668</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0452</v>
+        <v>0.0585</v>
       </c>
       <c r="J79" t="n">
-        <v>1.356</v>
+        <v>1.755</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0122</v>
+        <v>-0.0094</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.366</v>
+        <v>-0.282</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.97</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0635</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.905</v>
+        <v>-2.058</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.79</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2198</v>
+        <v>1.3317</v>
       </c>
       <c r="J82" t="n">
-        <v>28.0554</v>
+        <v>30.6291</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6138</v>
+        <v>0.6821</v>
       </c>
       <c r="J83" t="n">
-        <v>14.1174</v>
+        <v>15.6883</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3759</v>
+        <v>0.4054</v>
       </c>
       <c r="J84" t="n">
-        <v>8.6457</v>
+        <v>9.324199999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1773</v>
+        <v>0.1949</v>
       </c>
       <c r="J85" t="n">
-        <v>4.0779</v>
+        <v>4.4827</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5768</v>
+        <v>-0.5362</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.2664</v>
+        <v>-12.3326</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.08</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2408</v>
+        <v>0.2386</v>
       </c>
       <c r="J87" t="n">
-        <v>5.5384</v>
+        <v>5.4878</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.02</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0953</v>
+        <v>0.0945</v>
       </c>
       <c r="J88" t="n">
-        <v>2.1919</v>
+        <v>2.1735</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.01</v>
       </c>
       <c r="I89" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="J89" t="n">
-        <v>1.5088</v>
+        <v>1.4582</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1642</v>
+        <v>-0.1807</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.7766</v>
+        <v>-4.1561</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.44</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5616</v>
+        <v>-0.5644</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.9168</v>
+        <v>-12.9812</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4526</v>
+        <v>0.433</v>
       </c>
       <c r="J92" t="n">
-        <v>11.315</v>
+        <v>10.825</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1596</v>
+        <v>-0.1772</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.99</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1698</v>
+        <v>-0.1876</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.245</v>
+        <v>-4.69</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2184</v>
+        <v>-0.2364</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.46</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.47</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5344</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.2175</v>
+        <v>-13.36</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.53</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1691</v>
+        <v>1.1359</v>
       </c>
       <c r="J97" t="n">
-        <v>29.2275</v>
+        <v>28.3975</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8946</v>
+        <v>0.8439</v>
       </c>
       <c r="J98" t="n">
-        <v>22.365</v>
+        <v>21.0975</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.35</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8946</v>
+        <v>0.8439</v>
       </c>
       <c r="J99" t="n">
-        <v>22.365</v>
+        <v>21.0975</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5185</v>
       </c>
       <c r="J100" t="n">
-        <v>13.2175</v>
+        <v>12.9625</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6853</v>
+        <v>-0.6325</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.1325</v>
+        <v>-15.8125</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6264</v>
+        <v>0.5921</v>
       </c>
       <c r="J102" t="n">
-        <v>13.7808</v>
+        <v>13.0262</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0564</v>
+        <v>-0.0711</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.2408</v>
+        <v>-1.5642</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1701</v>
+        <v>-0.1877</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.7422</v>
+        <v>-4.1294</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2863</v>
+        <v>-0.3032</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.2986</v>
+        <v>-6.6704</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.37</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6194</v>
+        <v>-0.6191</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.6268</v>
+        <v>-13.6202</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.72</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3671</v>
+        <v>1.3529</v>
       </c>
       <c r="J107" t="n">
-        <v>30.0762</v>
+        <v>29.7638</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.72</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3671</v>
+        <v>1.3529</v>
       </c>
       <c r="J108" t="n">
-        <v>30.0762</v>
+        <v>29.7638</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.47</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0685</v>
+        <v>1.0303</v>
       </c>
       <c r="J109" t="n">
-        <v>23.507</v>
+        <v>22.6666</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.06</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1391</v>
+        <v>0.1682</v>
       </c>
       <c r="J110" t="n">
-        <v>3.0602</v>
+        <v>3.7004</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0936</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.0592</v>
+        <v>-1.4322</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.71</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2728</v>
+        <v>-0.2966</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.456</v>
+        <v>-5.932</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2728</v>
+        <v>-0.2966</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.456</v>
+        <v>-5.932</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.63</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3498</v>
+        <v>-0.3704</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.996</v>
+        <v>-7.408</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.58</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3936</v>
+        <v>-0.4125</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.872</v>
+        <v>-8.25</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5153</v>
+        <v>-0.5265</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.306</v>
+        <v>-10.53</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1517</v>
+        <v>1.1231</v>
       </c>
       <c r="J117" t="n">
-        <v>23.034</v>
+        <v>22.462</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.53</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1397</v>
+        <v>1.1101</v>
       </c>
       <c r="J118" t="n">
-        <v>22.794</v>
+        <v>22.202</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9827</v>
+        <v>0.9335</v>
       </c>
       <c r="J119" t="n">
-        <v>19.654</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.36</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8872</v>
+        <v>0.843</v>
       </c>
       <c r="J120" t="n">
-        <v>17.744</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.18</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4692</v>
+        <v>0.4721</v>
       </c>
       <c r="J121" t="n">
-        <v>9.384</v>
+        <v>9.442</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8882</v>
+        <v>0.7817</v>
       </c>
       <c r="J122" t="n">
-        <v>16.8758</v>
+        <v>14.8523</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.46</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.4914</v>
+        <v>-0.5064</v>
       </c>
       <c r="J123" t="n">
-        <v>-9.336600000000001</v>
+        <v>-9.621600000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.41</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5393</v>
+        <v>-0.5507</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.2467</v>
+        <v>-10.4633</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.31</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.637</v>
+        <v>-0.6402</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.103</v>
+        <v>-12.1638</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.3</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6468</v>
+        <v>-0.6492</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.2892</v>
+        <v>-12.3348</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.86</v>
       </c>
       <c r="I127" t="n">
-        <v>1.5015</v>
+        <v>1.4996</v>
       </c>
       <c r="J127" t="n">
-        <v>28.5285</v>
+        <v>28.4924</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.74</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3663</v>
+        <v>1.3565</v>
       </c>
       <c r="J128" t="n">
-        <v>25.9597</v>
+        <v>25.7735</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.51</v>
       </c>
       <c r="I129" t="n">
-        <v>1.1039</v>
+        <v>1.0739</v>
       </c>
       <c r="J129" t="n">
-        <v>20.9741</v>
+        <v>20.4041</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.4</v>
       </c>
       <c r="I130" t="n">
-        <v>0.9478</v>
+        <v>0.9025</v>
       </c>
       <c r="J130" t="n">
-        <v>18.0082</v>
+        <v>17.1475</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.13</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3133</v>
+        <v>0.336</v>
       </c>
       <c r="J131" t="n">
-        <v>5.9527</v>
+        <v>6.384</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.91</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.54</v>
+        <v>-2.0724</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.78</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2169</v>
+        <v>-0.2397</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.7718</v>
+        <v>-5.2734</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.77</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2272</v>
+        <v>-0.2497</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.9984</v>
+        <v>-5.4934</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.48</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4985</v>
+        <v>-0.5092</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.967</v>
+        <v>-11.2024</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.47</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5079</v>
+        <v>-0.518</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.1738</v>
+        <v>-11.396</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2923</v>
+        <v>1.2764</v>
       </c>
       <c r="J137" t="n">
-        <v>28.4306</v>
+        <v>28.0808</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.63</v>
       </c>
       <c r="I138" t="n">
-        <v>1.246</v>
+        <v>1.2269</v>
       </c>
       <c r="J138" t="n">
-        <v>27.412</v>
+        <v>26.9918</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
-        <v>1.118</v>
+        <v>1.0887</v>
       </c>
       <c r="J139" t="n">
-        <v>24.596</v>
+        <v>23.9514</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.48</v>
       </c>
       <c r="I140" t="n">
-        <v>1.0719</v>
+        <v>1.0366</v>
       </c>
       <c r="J140" t="n">
-        <v>23.5818</v>
+        <v>22.8052</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.348</v>
+        <v>0.366</v>
       </c>
       <c r="J141" t="n">
-        <v>7.656</v>
+        <v>8.052</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.502</v>
+        <v>0.4939</v>
       </c>
       <c r="J142" t="n">
-        <v>13.554</v>
+        <v>13.3353</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3374</v>
+        <v>0.3407</v>
       </c>
       <c r="J143" t="n">
-        <v>9.1098</v>
+        <v>9.1989</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0346</v>
+        <v>0.0412</v>
       </c>
       <c r="J144" t="n">
-        <v>0.9342</v>
+        <v>1.1124</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0385</v>
+        <v>-0.0446</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.0395</v>
+        <v>-1.2042</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2817</v>
+        <v>-0.2939</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.6059</v>
+        <v>-7.9353</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.99</v>
       </c>
       <c r="I147" t="n">
-        <v>1.7661</v>
+        <v>1.7584</v>
       </c>
       <c r="J147" t="n">
-        <v>47.6847</v>
+        <v>47.4768</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.26</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7149</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>19.3023</v>
+        <v>18.3843</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.331</v>
+        <v>-0.3162</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.936999999999999</v>
+        <v>-8.5374</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5837</v>
+        <v>-0.5462</v>
       </c>
       <c r="J150" t="n">
-        <v>-15.7599</v>
+        <v>-14.7474</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8144</v>
+        <v>-0.7506</v>
       </c>
       <c r="J151" t="n">
-        <v>-21.9888</v>
+        <v>-20.2662</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4251</v>
+        <v>0.4238</v>
       </c>
       <c r="J152" t="n">
-        <v>12.3279</v>
+        <v>12.2902</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3887</v>
+        <v>0.3898</v>
       </c>
       <c r="J153" t="n">
-        <v>11.2723</v>
+        <v>11.3042</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2756</v>
+        <v>0.2829</v>
       </c>
       <c r="J154" t="n">
-        <v>7.9924</v>
+        <v>8.2041</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.96</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0678</v>
+        <v>-0.0761</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.9662</v>
+        <v>-2.2069</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.77</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.274</v>
+        <v>-0.2858</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.946</v>
+        <v>-8.2882</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.24</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6551</v>
       </c>
       <c r="J157" t="n">
-        <v>20.039</v>
+        <v>18.9979</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.19</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5655</v>
+        <v>0.5437</v>
       </c>
       <c r="J158" t="n">
-        <v>16.3995</v>
+        <v>15.7673</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.1</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3271</v>
+        <v>0.327</v>
       </c>
       <c r="J159" t="n">
-        <v>9.485900000000001</v>
+        <v>9.483000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.271</v>
+        <v>0.2746</v>
       </c>
       <c r="J160" t="n">
-        <v>7.859</v>
+        <v>7.9634</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.77</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6711</v>
       </c>
       <c r="J161" t="n">
-        <v>-20.8887</v>
+        <v>-19.4619</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.96</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.037</v>
+        <v>-0.0523</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.888</v>
+        <v>-1.2552</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.88</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1341</v>
+        <v>-0.1524</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.2184</v>
+        <v>-3.6576</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.145</v>
+        <v>-0.1635</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.48</v>
+        <v>-3.924</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.78</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2345</v>
+        <v>-0.2531</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.628</v>
+        <v>-6.0744</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.52</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4793</v>
+        <v>-0.4884</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.5032</v>
+        <v>-11.7216</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.66</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3247</v>
+        <v>1.3027</v>
       </c>
       <c r="J167" t="n">
-        <v>31.7928</v>
+        <v>31.2648</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.32</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8226</v>
+        <v>0.7816</v>
       </c>
       <c r="J168" t="n">
-        <v>19.7424</v>
+        <v>18.7584</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.26</v>
       </c>
       <c r="I169" t="n">
-        <v>0.6893</v>
+        <v>0.6634</v>
       </c>
       <c r="J169" t="n">
-        <v>16.5432</v>
+        <v>15.9216</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.15</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4226</v>
+        <v>0.4236</v>
       </c>
       <c r="J170" t="n">
-        <v>10.1424</v>
+        <v>10.1664</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2988</v>
+        <v>-0.2791</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.1712</v>
+        <v>-6.6984</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0189</v>
+        <v>1.0117</v>
       </c>
       <c r="J172" t="n">
-        <v>17.3213</v>
+        <v>17.1989</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.71</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7713</v>
+        <v>0.7739</v>
       </c>
       <c r="J173" t="n">
-        <v>13.1121</v>
+        <v>13.1563</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.6</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6681</v>
+        <v>0.6772</v>
       </c>
       <c r="J174" t="n">
-        <v>11.3577</v>
+        <v>11.5124</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.6</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6681</v>
+        <v>0.6772</v>
       </c>
       <c r="J175" t="n">
-        <v>11.3577</v>
+        <v>11.5124</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.54</v>
       </c>
       <c r="I176" t="n">
-        <v>0.6087</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>10.3479</v>
+        <v>10.5655</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.82</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1154</v>
+        <v>-0.1515</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.9618</v>
+        <v>-2.5755</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.7</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2545</v>
+        <v>-0.2841</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.3265</v>
+        <v>-4.8297</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.67</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2869</v>
+        <v>-0.3147</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.8773</v>
+        <v>-5.3499</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.26</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6837</v>
+        <v>-0.6831</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.6229</v>
+        <v>-11.6127</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.19</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7539</v>
+        <v>-0.7466</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.8163</v>
+        <v>-12.6922</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.54</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9698</v>
+        <v>0.924</v>
       </c>
       <c r="J182" t="n">
-        <v>58.188</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.06</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1481</v>
+        <v>0.1605</v>
       </c>
       <c r="J183" t="n">
-        <v>8.885999999999999</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.103</v>
+        <v>0.1153</v>
       </c>
       <c r="J184" t="n">
-        <v>6.18</v>
+        <v>6.918</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0978</v>
+        <v>-0.1065</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.868</v>
+        <v>-6.39</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.88</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1663</v>
+        <v>-0.1772</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.978</v>
+        <v>-10.632</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.17</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5256</v>
+        <v>0.5056</v>
       </c>
       <c r="J187" t="n">
-        <v>31.536</v>
+        <v>30.336</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3355</v>
+        <v>0.3328</v>
       </c>
       <c r="J188" t="n">
-        <v>20.13</v>
+        <v>19.968</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0083</v>
+        <v>-0.0056</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.498</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.98</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1035</v>
+        <v>-0.1063</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.21</v>
+        <v>-6.378</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1752</v>
+        <v>-0.1762</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.512</v>
+        <v>-10.572</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.43</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8264</v>
+        <v>0.7875</v>
       </c>
       <c r="J192" t="n">
-        <v>28.0976</v>
+        <v>26.775</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5203</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>17.6902</v>
+        <v>17.3604</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.93</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1028</v>
+        <v>-0.1136</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.4952</v>
+        <v>-3.8624</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1259</v>
+        <v>-0.1376</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.2806</v>
+        <v>-4.6784</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.61</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4227</v>
+        <v>-0.4306</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.3718</v>
+        <v>-14.6404</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1133</v>
+        <v>1.0718</v>
       </c>
       <c r="J197" t="n">
-        <v>37.8522</v>
+        <v>36.4412</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.34</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8988</v>
+        <v>0.8428</v>
       </c>
       <c r="J198" t="n">
-        <v>30.5592</v>
+        <v>28.6552</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4448</v>
+        <v>0.4389</v>
       </c>
       <c r="J199" t="n">
-        <v>15.1232</v>
+        <v>14.9226</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3337</v>
+        <v>-0.318</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.3458</v>
+        <v>-10.812</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3635</v>
+        <v>-0.3456</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.359</v>
+        <v>-11.7504</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.25</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5275</v>
+        <v>0.498</v>
       </c>
       <c r="J202" t="n">
-        <v>11.0775</v>
+        <v>10.458</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.9</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0934</v>
+        <v>-0.1154</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.9614</v>
+        <v>-2.4234</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.65</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3458</v>
+        <v>-0.3637</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.2618</v>
+        <v>-7.6377</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.43</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5511</v>
+        <v>-0.5574</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.5731</v>
+        <v>-11.7054</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.37</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6068</v>
+        <v>-0.609</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.7428</v>
+        <v>-12.789</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.7</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7861</v>
+        <v>0.7834</v>
       </c>
       <c r="J207" t="n">
-        <v>16.5081</v>
+        <v>16.4514</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.6</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6866</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>14.4186</v>
+        <v>14.511</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.38</v>
       </c>
       <c r="I209" t="n">
-        <v>0.463</v>
+        <v>0.4795</v>
       </c>
       <c r="J209" t="n">
-        <v>9.723000000000001</v>
+        <v>10.0695</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.36</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4414</v>
+        <v>0.4589</v>
       </c>
       <c r="J210" t="n">
-        <v>9.269399999999999</v>
+        <v>9.636900000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.25</v>
       </c>
       <c r="I211" t="n">
-        <v>0.3162</v>
+        <v>0.3384</v>
       </c>
       <c r="J211" t="n">
-        <v>6.6402</v>
+        <v>7.1064</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.4</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0341</v>
+        <v>0.9755</v>
       </c>
       <c r="J212" t="n">
-        <v>28.9548</v>
+        <v>27.314</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.403</v>
+        <v>0.3982</v>
       </c>
       <c r="J213" t="n">
-        <v>11.284</v>
+        <v>11.1496</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.06</v>
       </c>
       <c r="I214" t="n">
-        <v>0.208</v>
+        <v>0.2162</v>
       </c>
       <c r="J214" t="n">
-        <v>5.824</v>
+        <v>6.0536</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.208</v>
+        <v>0.2162</v>
       </c>
       <c r="J215" t="n">
-        <v>5.824</v>
+        <v>6.0536</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5172</v>
+        <v>-0.489</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.4816</v>
+        <v>-13.692</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.586</v>
+        <v>0.5684</v>
       </c>
       <c r="J217" t="n">
-        <v>16.408</v>
+        <v>15.9152</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.22</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4786</v>
+        <v>0.47</v>
       </c>
       <c r="J218" t="n">
-        <v>13.4008</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.099</v>
+        <v>-0.1107</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.772</v>
+        <v>-3.0996</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.77</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2676</v>
+        <v>-0.2809</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.4928</v>
+        <v>-7.8652</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.75</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2871</v>
+        <v>-0.3</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.0388</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.63</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3328</v>
+        <v>1.3035</v>
       </c>
       <c r="J222" t="n">
-        <v>54.6448</v>
+        <v>53.4435</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.21</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6031</v>
+        <v>0.5798</v>
       </c>
       <c r="J223" t="n">
-        <v>24.7271</v>
+        <v>23.7718</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2348</v>
+        <v>0.2424</v>
       </c>
       <c r="J224" t="n">
-        <v>9.626799999999999</v>
+        <v>9.9384</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2285</v>
+        <v>-0.222</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.368499999999999</v>
+        <v>-9.102</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8559</v>
+        <v>-0.7883</v>
       </c>
       <c r="J226" t="n">
-        <v>-35.0919</v>
+        <v>-32.3203</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.52</v>
       </c>
       <c r="I227" t="n">
-        <v>0.9502</v>
+        <v>0.9031</v>
       </c>
       <c r="J227" t="n">
-        <v>38.9582</v>
+        <v>37.0271</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2708</v>
+        <v>0.2795</v>
       </c>
       <c r="J228" t="n">
-        <v>11.1028</v>
+        <v>11.4595</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0569</v>
+        <v>-0.0635</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.3329</v>
+        <v>-2.6035</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1307</v>
+        <v>-0.1414</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.3587</v>
+        <v>-5.7974</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2165</v>
+        <v>-0.2284</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.8765</v>
+        <v>-9.3644</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.76</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2242</v>
+        <v>-0.2493</v>
       </c>
       <c r="J232" t="n">
-        <v>-4.484</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.7</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2857</v>
+        <v>-0.3085</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.714</v>
+        <v>-6.17</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.59</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3865</v>
+        <v>-0.4053</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.73</v>
+        <v>-8.106</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.58</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3956</v>
+        <v>-0.414</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.912</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.51</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4608</v>
+        <v>-0.4754</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.215999999999999</v>
+        <v>-9.507999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.62</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7076</v>
+        <v>0.7104</v>
       </c>
       <c r="J237" t="n">
-        <v>14.152</v>
+        <v>14.208</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.62</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7076</v>
+        <v>0.7104</v>
       </c>
       <c r="J238" t="n">
-        <v>14.152</v>
+        <v>14.208</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.53</v>
       </c>
       <c r="I239" t="n">
-        <v>0.617</v>
+        <v>0.6256</v>
       </c>
       <c r="J239" t="n">
-        <v>12.34</v>
+        <v>12.512</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.37</v>
       </c>
       <c r="I240" t="n">
-        <v>0.453</v>
+        <v>0.4698</v>
       </c>
       <c r="J240" t="n">
-        <v>9.06</v>
+        <v>9.396000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.11</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1379</v>
+        <v>0.1628</v>
       </c>
       <c r="J241" t="n">
-        <v>2.758</v>
+        <v>3.256</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.51</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1985</v>
+        <v>1.1571</v>
       </c>
       <c r="J242" t="n">
-        <v>40.749</v>
+        <v>39.3414</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.18</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5474</v>
+        <v>0.5259</v>
       </c>
       <c r="J243" t="n">
-        <v>18.6116</v>
+        <v>17.8806</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0432</v>
+        <v>0.0518</v>
       </c>
       <c r="J244" t="n">
-        <v>1.4688</v>
+        <v>1.7612</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6109</v>
+        <v>-0.5754</v>
       </c>
       <c r="J245" t="n">
-        <v>-20.7706</v>
+        <v>-19.5636</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.76</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7396</v>
+        <v>-0.6892</v>
       </c>
       <c r="J246" t="n">
-        <v>-25.1464</v>
+        <v>-23.4328</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.2</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4279</v>
+        <v>0.4258</v>
       </c>
       <c r="J247" t="n">
-        <v>14.5486</v>
+        <v>14.4772</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.218</v>
+        <v>0.227</v>
       </c>
       <c r="J248" t="n">
-        <v>7.412</v>
+        <v>7.718</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1765</v>
+        <v>0.1865</v>
       </c>
       <c r="J249" t="n">
-        <v>6.001</v>
+        <v>6.341</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0919</v>
+        <v>-0.1019</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.1246</v>
+        <v>-3.4646</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.88</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1602</v>
+        <v>-0.1725</v>
       </c>
       <c r="J251" t="n">
-        <v>-5.4468</v>
+        <v>-5.865</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.37</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9603</v>
+        <v>0.9003</v>
       </c>
       <c r="J252" t="n">
-        <v>27.8487</v>
+        <v>26.1087</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.34</v>
       </c>
       <c r="I253" t="n">
-        <v>0.896</v>
+        <v>0.8408</v>
       </c>
       <c r="J253" t="n">
-        <v>25.984</v>
+        <v>24.3832</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.16</v>
       </c>
       <c r="I254" t="n">
-        <v>0.4686</v>
+        <v>0.4608</v>
       </c>
       <c r="J254" t="n">
-        <v>13.5894</v>
+        <v>13.3632</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.11</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3381</v>
+        <v>0.3413</v>
       </c>
       <c r="J255" t="n">
-        <v>9.8049</v>
+        <v>9.8977</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.85</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5347</v>
+        <v>-0.5013</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.5063</v>
+        <v>-14.5377</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7083</v>
+        <v>0.679</v>
       </c>
       <c r="J257" t="n">
-        <v>20.5407</v>
+        <v>19.691</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2698</v>
+        <v>0.2742</v>
       </c>
       <c r="J258" t="n">
-        <v>7.8242</v>
+        <v>7.9518</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.92</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1104</v>
+        <v>-0.1226</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.2016</v>
+        <v>-3.5554</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.9</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1329</v>
+        <v>-0.1459</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.8541</v>
+        <v>-4.2311</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.66</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3725</v>
+        <v>-0.383</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.8025</v>
+        <v>-11.107</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.56</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6892</v>
+        <v>0.6861</v>
       </c>
       <c r="J262" t="n">
-        <v>16.5408</v>
+        <v>16.4664</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3644</v>
+        <v>0.3797</v>
       </c>
       <c r="J263" t="n">
-        <v>8.7456</v>
+        <v>9.1128</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2936</v>
+        <v>0.3108</v>
       </c>
       <c r="J264" t="n">
-        <v>7.0464</v>
+        <v>7.4592</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0185</v>
+        <v>-0.0143</v>
       </c>
       <c r="J265" t="n">
-        <v>-0.444</v>
+        <v>-0.3432</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.95</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1018</v>
       </c>
       <c r="J266" t="n">
-        <v>-2.3088</v>
+        <v>-2.4432</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.01</v>
       </c>
       <c r="I267" t="n">
-        <v>0.0548</v>
+        <v>0.0531</v>
       </c>
       <c r="J267" t="n">
-        <v>1.3152</v>
+        <v>1.2744</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1</v>
       </c>
       <c r="I268" t="n">
-        <v>0.0245</v>
+        <v>0.0181</v>
       </c>
       <c r="J268" t="n">
-        <v>0.588</v>
+        <v>0.4344</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1826</v>
+        <v>-0.1997</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.3824</v>
+        <v>-4.7928</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2224</v>
+        <v>-0.2395</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.3376</v>
+        <v>-5.748</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.67</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3479</v>
+        <v>-0.362</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.349600000000001</v>
+        <v>-8.688000000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8046</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="J272" t="n">
-        <v>23.3334</v>
+        <v>22.1444</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.01</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0439</v>
+        <v>0.0478</v>
       </c>
       <c r="J273" t="n">
-        <v>1.2731</v>
+        <v>1.3862</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.91</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1192</v>
+        <v>-0.1324</v>
       </c>
       <c r="J274" t="n">
-        <v>-3.4568</v>
+        <v>-3.8396</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.85</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1838</v>
+        <v>-0.1982</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.3302</v>
+        <v>-5.7478</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.65</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3791</v>
+        <v>-0.3899</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.9939</v>
+        <v>-11.3071</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.5</v>
       </c>
       <c r="I277" t="n">
-        <v>1.142</v>
+        <v>1.1047</v>
       </c>
       <c r="J277" t="n">
-        <v>33.118</v>
+        <v>32.0363</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.84</v>
+        <v>0.7936</v>
       </c>
       <c r="J278" t="n">
-        <v>24.36</v>
+        <v>23.0144</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5838</v>
+        <v>0.5665</v>
       </c>
       <c r="J279" t="n">
-        <v>16.9302</v>
+        <v>16.4285</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1045</v>
       </c>
       <c r="J280" t="n">
-        <v>2.465</v>
+        <v>3.0305</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.93</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3134</v>
+        <v>-0.2968</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.0886</v>
+        <v>-8.607200000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6481</v>
+        <v>0.5955</v>
       </c>
       <c r="J282" t="n">
-        <v>14.2582</v>
+        <v>13.101</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.74</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2602</v>
+        <v>-0.2812</v>
       </c>
       <c r="J283" t="n">
-        <v>-5.7244</v>
+        <v>-6.1864</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.306</v>
+        <v>-0.3259</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.732</v>
+        <v>-7.1698</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.48</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5011</v>
+        <v>-0.5113</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.0242</v>
+        <v>-11.2486</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.36</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6132</v>
+        <v>-0.6153</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.4904</v>
+        <v>-13.5366</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1336</v>
+        <v>1.1023</v>
       </c>
       <c r="J287" t="n">
-        <v>24.9392</v>
+        <v>24.2506</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1092</v>
+        <v>1.0758</v>
       </c>
       <c r="J288" t="n">
-        <v>24.4024</v>
+        <v>23.6676</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.45</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0471</v>
+        <v>1.0039</v>
       </c>
       <c r="J289" t="n">
-        <v>23.0362</v>
+        <v>22.0858</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.31</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7852</v>
+        <v>0.7518</v>
       </c>
       <c r="J290" t="n">
-        <v>17.2744</v>
+        <v>16.5396</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I291" t="n">
-        <v>0.0806</v>
+        <v>0.1108</v>
       </c>
       <c r="J291" t="n">
-        <v>1.7732</v>
+        <v>2.4376</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.53</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1861</v>
+        <v>1.1509</v>
       </c>
       <c r="J292" t="n">
-        <v>33.2108</v>
+        <v>32.2252</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1087</v>
+        <v>1.0676</v>
       </c>
       <c r="J293" t="n">
-        <v>31.0436</v>
+        <v>29.8928</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.07</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2207</v>
+        <v>0.2327</v>
       </c>
       <c r="J294" t="n">
-        <v>6.1796</v>
+        <v>6.5156</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.98</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1386</v>
+        <v>-0.1306</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.8808</v>
+        <v>-3.6568</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5908</v>
+        <v>-0.5512</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.5424</v>
+        <v>-15.4336</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.3</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6282</v>
       </c>
       <c r="J297" t="n">
-        <v>18.4464</v>
+        <v>17.5896</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4742</v>
+        <v>0.4598</v>
       </c>
       <c r="J298" t="n">
-        <v>13.2776</v>
+        <v>12.8744</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2176</v>
+        <v>-0.2336</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.0928</v>
+        <v>-6.5408</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.7</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3249</v>
+        <v>-0.3388</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.097200000000001</v>
+        <v>-9.4864</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.52</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.492</v>
+        <v>-0.4985</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.776</v>
+        <v>-13.958</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.5</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1714</v>
+        <v>1.1307</v>
       </c>
       <c r="J302" t="n">
-        <v>42.1704</v>
+        <v>40.7052</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.36</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9659</v>
+        <v>0.901</v>
       </c>
       <c r="J303" t="n">
-        <v>34.7724</v>
+        <v>32.436</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.02</v>
       </c>
       <c r="I304" t="n">
-        <v>0.0741</v>
+        <v>0.0862</v>
       </c>
       <c r="J304" t="n">
-        <v>2.6676</v>
+        <v>3.1032</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4883</v>
+        <v>-0.4632</v>
       </c>
       <c r="J305" t="n">
-        <v>-17.5788</v>
+        <v>-16.6752</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.8256</v>
+        <v>-0.7627</v>
       </c>
       <c r="J306" t="n">
-        <v>-29.7216</v>
+        <v>-27.4572</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.22</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4651</v>
+        <v>0.4601</v>
       </c>
       <c r="J307" t="n">
-        <v>16.7436</v>
+        <v>16.5636</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.06</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1557</v>
+        <v>0.1658</v>
       </c>
       <c r="J308" t="n">
-        <v>5.6052</v>
+        <v>5.9688</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1337</v>
+        <v>0.1439</v>
       </c>
       <c r="J309" t="n">
-        <v>4.8132</v>
+        <v>5.1804</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.99</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.0232</v>
+        <v>-0.0273</v>
       </c>
       <c r="J310" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.9828</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.84</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.202</v>
+        <v>-0.2148</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.272</v>
+        <v>-7.7328</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.31</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8542</v>
+        <v>0.7994</v>
       </c>
       <c r="J312" t="n">
-        <v>25.626</v>
+        <v>23.982</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4835</v>
+        <v>0.471</v>
       </c>
       <c r="J313" t="n">
-        <v>14.505</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2399</v>
+        <v>0.2458</v>
       </c>
       <c r="J314" t="n">
-        <v>7.197</v>
+        <v>7.374</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.01</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0338</v>
+        <v>0.0454</v>
       </c>
       <c r="J315" t="n">
-        <v>1.014</v>
+        <v>1.362</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3458</v>
+        <v>-0.3332</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.374</v>
+        <v>-9.996</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.32</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6633</v>
+        <v>0.6373</v>
       </c>
       <c r="J317" t="n">
-        <v>19.899</v>
+        <v>19.119</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.233</v>
+        <v>0.2379</v>
       </c>
       <c r="J318" t="n">
-        <v>6.99</v>
+        <v>7.137</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.89</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1421</v>
+        <v>-0.1558</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.263</v>
+        <v>-4.674</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.78</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2556</v>
+        <v>-0.2695</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.668</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.78</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2556</v>
+        <v>-0.2695</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.668</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.5</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1057</v>
+        <v>1.0727</v>
       </c>
       <c r="J322" t="n">
-        <v>25.4311</v>
+        <v>24.6721</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>1.016</v>
+        <v>0.9688</v>
       </c>
       <c r="J323" t="n">
-        <v>23.368</v>
+        <v>22.2824</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.42</v>
       </c>
       <c r="I324" t="n">
-        <v>1.0006</v>
+        <v>0.952</v>
       </c>
       <c r="J324" t="n">
-        <v>23.0138</v>
+        <v>21.896</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.37</v>
       </c>
       <c r="I325" t="n">
-        <v>0.9105</v>
+        <v>0.8633</v>
       </c>
       <c r="J325" t="n">
-        <v>20.9415</v>
+        <v>19.8559</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.22</v>
       </c>
       <c r="I326" t="n">
-        <v>0.5715</v>
+        <v>0.5632</v>
       </c>
       <c r="J326" t="n">
-        <v>13.1445</v>
+        <v>12.9536</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.02</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1518</v>
+        <v>0.136</v>
       </c>
       <c r="J327" t="n">
-        <v>3.4914</v>
+        <v>3.128</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1998</v>
+        <v>-0.22</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.5954</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.73</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2757</v>
+        <v>-0.295</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.3411</v>
+        <v>-6.785</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.7</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3037</v>
+        <v>-0.3223</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.9851</v>
+        <v>-7.4129</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.5</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4907</v>
+        <v>-0.5003</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.2861</v>
+        <v>-11.5069</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3190/event_3190_evp_summary.xlsx
+++ b/database/event/3190/event_3190_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6606</v>
+        <v>6.5069</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6152</v>
+        <v>0.601</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4078</v>
+        <v>2.3584</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6606</v>
+        <v>6.5069</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8655</v>
+        <v>3.7191</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7951</v>
+        <v>2.7878</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8594</v>
+        <v>7.5205</v>
       </c>
       <c r="I2" t="n">
-        <v>4.244</v>
+        <v>4.2225</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7951</v>
+        <v>2.7878</v>
       </c>
       <c r="K2" t="n">
         <v>160</v>
@@ -529,7 +529,7 @@
         <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>7.039099999999999</v>
+        <v>7.0103</v>
       </c>
       <c r="N2" t="n">
         <v>291</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2263</v>
+        <v>4.0623</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3903</v>
+        <v>0.3752</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2997</v>
+        <v>1.2448</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2263</v>
+        <v>4.0623</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0733</v>
+        <v>2.4233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.153</v>
+        <v>1.639</v>
       </c>
       <c r="H3" t="n">
-        <v>8.545199999999999</v>
+        <v>2.6554</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6144</v>
+        <v>1.4909</v>
       </c>
       <c r="J3" t="n">
-        <v>0.153</v>
+        <v>1.639</v>
       </c>
       <c r="K3" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="M3" t="n">
-        <v>4.767399999999999</v>
+        <v>3.1299</v>
       </c>
       <c r="N3" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9923</v>
+        <v>3.9721</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3687</v>
+        <v>0.3669</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1932</v>
+        <v>1.2037</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9923</v>
+        <v>3.9721</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4823</v>
+        <v>3.8601</v>
       </c>
       <c r="G4" t="n">
-        <v>0.51</v>
+        <v>0.112</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5954</v>
+        <v>8.049899999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5614</v>
+        <v>4.5198</v>
       </c>
       <c r="J4" t="n">
-        <v>0.51</v>
+        <v>0.112</v>
       </c>
       <c r="K4" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="L4" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0714</v>
+        <v>4.6318</v>
       </c>
       <c r="N4" t="n">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9646</v>
+        <v>3.8358</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3662</v>
+        <v>0.3543</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1806</v>
+        <v>1.1416</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9646</v>
+        <v>3.8358</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3679</v>
+        <v>3.302</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5967</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2179</v>
+        <v>5.9547</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3576</v>
+        <v>3.3434</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5967</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>194</v>
@@ -667,7 +667,7 @@
         <v>81</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9543</v>
+        <v>3.8772</v>
       </c>
       <c r="N5" t="n">
         <v>275</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9249</v>
+        <v>3.8017</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3625</v>
+        <v>0.3511</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1625</v>
+        <v>1.1261</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9249</v>
+        <v>3.8017</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3194</v>
+        <v>3.3886</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6055</v>
+        <v>0.4131</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7584</v>
+        <v>6.2796</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4895</v>
+        <v>3.5258</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6055</v>
+        <v>0.4131</v>
       </c>
       <c r="K6" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="L6" t="n">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="M6" t="n">
-        <v>3.095</v>
+        <v>3.9389</v>
       </c>
       <c r="N6" t="n">
-        <v>291</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7336</v>
+        <v>3.7171</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3448</v>
+        <v>0.3433</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0754</v>
+        <v>1.0875</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7336</v>
+        <v>3.7171</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0705</v>
+        <v>2.6618</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6631</v>
+        <v>1.0553</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2365</v>
+        <v>3.5509</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8277</v>
+        <v>1.9937</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6631</v>
+        <v>1.0553</v>
       </c>
       <c r="K7" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="L7" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4908</v>
+        <v>3.049</v>
       </c>
       <c r="N7" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7137</v>
+        <v>3.668</v>
       </c>
       <c r="C8" t="n">
-        <v>0.343</v>
+        <v>0.3388</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0663</v>
+        <v>1.0652</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7137</v>
+        <v>3.668</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6392</v>
+        <v>3.0524</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0745</v>
+        <v>0.6156</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8134</v>
+        <v>5.0174</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0592</v>
+        <v>2.8171</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0745</v>
+        <v>0.6156</v>
       </c>
       <c r="K8" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="L8" t="n">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1337</v>
+        <v>3.4327</v>
       </c>
       <c r="N8" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5434</v>
+        <v>3.628</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3273</v>
+        <v>0.3351</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9888</v>
+        <v>1.0469</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5434</v>
+        <v>3.628</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5111</v>
+        <v>0.6298</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0323</v>
+        <v>2.9982</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5111</v>
+        <v>0.6298</v>
       </c>
       <c r="I9" t="n">
-        <v>0.276</v>
+        <v>0.3536</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0323</v>
+        <v>2.9982</v>
       </c>
       <c r="K9" t="n">
         <v>160</v>
@@ -851,7 +851,7 @@
         <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3083</v>
+        <v>3.3518</v>
       </c>
       <c r="N9" t="n">
         <v>291</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.472</v>
+        <v>3.3555</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3207</v>
+        <v>0.3099</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9563</v>
+        <v>0.9228</v>
       </c>
       <c r="E10" t="n">
-        <v>3.472</v>
+        <v>3.3555</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2428</v>
+        <v>3.1685</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2292</v>
+        <v>0.187</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8049</v>
+        <v>5.4535</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1346</v>
+        <v>3.062</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2292</v>
+        <v>0.187</v>
       </c>
       <c r="K10" t="n">
         <v>211</v>
@@ -897,7 +897,7 @@
         <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3638</v>
+        <v>3.249</v>
       </c>
       <c r="N10" t="n">
         <v>264</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0367</v>
+        <v>3.0927</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2805</v>
+        <v>0.2856</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7582</v>
+        <v>0.8031</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0367</v>
+        <v>3.0927</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6618</v>
+        <v>2.7256</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3749</v>
+        <v>0.3671</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8882</v>
+        <v>3.7906</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0996</v>
+        <v>2.1283</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3749</v>
+        <v>0.3671</v>
       </c>
       <c r="K11" t="n">
         <v>211</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4745</v>
+        <v>2.4954</v>
       </c>
       <c r="N11" t="n">
         <v>264</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7132</v>
+        <v>2.7052</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2506</v>
+        <v>0.2499</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6109</v>
+        <v>0.6266</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7132</v>
+        <v>2.7052</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7321</v>
+        <v>2.7752</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0189</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1199</v>
+        <v>3.9765</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2247</v>
+        <v>2.2327</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0189</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2058</v>
+        <v>2.1627</v>
       </c>
       <c r="N12" t="n">
-        <v>275</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6558</v>
+        <v>2.6774</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2453</v>
+        <v>0.2473</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5848</v>
+        <v>0.6139</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6558</v>
+        <v>2.6774</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7058</v>
+        <v>2.7297</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.05</v>
+        <v>-0.0523</v>
       </c>
       <c r="H13" t="n">
-        <v>4.0332</v>
+        <v>3.806</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1779</v>
+        <v>2.137</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.05</v>
+        <v>-0.0523</v>
       </c>
       <c r="K13" t="n">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="L13" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1279</v>
+        <v>2.0847</v>
       </c>
       <c r="N13" t="n">
-        <v>235</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5133</v>
+        <v>2.4686</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2321</v>
+        <v>0.228</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5199</v>
+        <v>0.5188</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5133</v>
+        <v>2.4686</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1463</v>
+        <v>3.465</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.633</v>
+        <v>-0.9964</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4868</v>
+        <v>6.5665</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9628</v>
+        <v>3.6869</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.633</v>
+        <v>-0.9964</v>
       </c>
       <c r="K14" t="n">
-        <v>211</v>
+        <v>132</v>
       </c>
       <c r="L14" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3298</v>
+        <v>2.6905</v>
       </c>
       <c r="N14" t="n">
-        <v>264</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5061</v>
+        <v>2.4524</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2315</v>
+        <v>0.2265</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5061</v>
+        <v>2.4524</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5396</v>
+        <v>3.0807</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0335</v>
+        <v>-0.6283</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7844</v>
+        <v>5.1236</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6635</v>
+        <v>2.8768</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.0335</v>
+        <v>-0.6283</v>
       </c>
       <c r="K15" t="n">
-        <v>132</v>
+        <v>211</v>
       </c>
       <c r="L15" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="M15" t="n">
-        <v>2.63</v>
+        <v>2.2485</v>
       </c>
       <c r="N15" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3627</v>
+        <v>2.2401</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2182</v>
+        <v>0.2069</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4513</v>
+        <v>0.4147</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3627</v>
+        <v>2.2401</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3627</v>
+        <v>2.2401</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4462</v>
+        <v>2.2401</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4462</v>
+        <v>2.2401</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4462</v>
+        <v>2.2401</v>
       </c>
       <c r="N16" t="n">
         <v>165</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0221</v>
+        <v>1.8251</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1868</v>
+        <v>0.1686</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2963</v>
+        <v>0.2256</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0221</v>
+        <v>1.8251</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0221</v>
+        <v>1.8251</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0221</v>
+        <v>1.8251</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0221</v>
+        <v>1.8251</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0221</v>
+        <v>1.8251</v>
       </c>
       <c r="N17" t="n">
         <v>175</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9836</v>
+        <v>1.7615</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1832</v>
+        <v>0.1627</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2788</v>
+        <v>0.1967</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9836</v>
+        <v>1.7615</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9836</v>
+        <v>1.7615</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9836</v>
+        <v>1.7615</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9836</v>
+        <v>1.7615</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9836</v>
+        <v>1.7615</v>
       </c>
       <c r="N18" t="n">
         <v>165</v>
@@ -1274,78 +1274,78 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8009</v>
+        <v>1.7312</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1663</v>
+        <v>0.1599</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1956</v>
+        <v>0.1829</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8009</v>
+        <v>1.7312</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8009</v>
+        <v>2.3479</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6167</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8009</v>
+        <v>2.3723</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8009</v>
+        <v>1.332</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6167</v>
       </c>
       <c r="K19" t="n">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8009</v>
+        <v>0.7153</v>
       </c>
       <c r="N19" t="n">
-        <v>241</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7923</v>
+        <v>1.6703</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1655</v>
+        <v>0.1543</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1917</v>
+        <v>0.1551</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7923</v>
+        <v>1.6703</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7923</v>
+        <v>1.6703</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7923</v>
+        <v>1.6703</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7923</v>
+        <v>1.6703</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7923</v>
+        <v>1.6703</v>
       </c>
       <c r="N20" t="n">
         <v>241</v>
@@ -1366,127 +1366,127 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6408</v>
+        <v>1.6499</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1515</v>
+        <v>0.1524</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1227</v>
+        <v>0.1458</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6408</v>
+        <v>1.6499</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6408</v>
+        <v>1.6499</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6408</v>
+        <v>1.6499</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6408</v>
+        <v>1.6499</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6408</v>
+        <v>1.6499</v>
       </c>
       <c r="N21" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6034</v>
+        <v>1.4985</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1481</v>
+        <v>0.1384</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1057</v>
+        <v>0.0769</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6034</v>
+        <v>1.4985</v>
       </c>
       <c r="F22" t="n">
-        <v>2.269</v>
+        <v>1.4985</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6656</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5922</v>
+        <v>1.4985</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3998</v>
+        <v>1.4985</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6656</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="L22" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7342</v>
+        <v>1.4985</v>
       </c>
       <c r="N22" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3465</v>
+        <v>1.3232</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1244</v>
+        <v>0.1222</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0112</v>
+        <v>-0.003</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3465</v>
+        <v>1.3232</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0769</v>
+        <v>0.4143</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7304</v>
+        <v>0.9089</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0769</v>
+        <v>0.4143</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1215</v>
+        <v>0.2326</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7304</v>
+        <v>0.9089</v>
       </c>
       <c r="K23" t="n">
         <v>132</v>
@@ -1495,7 +1495,7 @@
         <v>103</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3910999999999999</v>
+        <v>1.1415</v>
       </c>
       <c r="N23" t="n">
         <v>235</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2267</v>
+        <v>1.3045</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1133</v>
+        <v>0.1205</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0658</v>
+        <v>-0.0115</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2267</v>
+        <v>1.3045</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3085</v>
+        <v>1.9928</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9182</v>
+        <v>-0.6883</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3085</v>
+        <v>1.9928</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1666</v>
+        <v>1.1189</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9182</v>
+        <v>-0.6883</v>
       </c>
       <c r="K24" t="n">
         <v>132</v>
@@ -1541,7 +1541,7 @@
         <v>103</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0848</v>
+        <v>0.4306</v>
       </c>
       <c r="N24" t="n">
         <v>235</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>COLDYY1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2011</v>
+        <v>1.1158</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1109</v>
+        <v>0.1031</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0774</v>
+        <v>-0.0975</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2011</v>
+        <v>1.1158</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2011</v>
+        <v>1.1158</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2011</v>
+        <v>1.1158</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2011</v>
+        <v>1.1158</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2011</v>
+        <v>1.1158</v>
       </c>
       <c r="N25" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COLDYY1</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.1196</v>
+        <v>1.0134</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1034</v>
+        <v>0.0936</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1145</v>
+        <v>-0.1441</v>
       </c>
       <c r="E26" t="n">
-        <v>1.1196</v>
+        <v>1.0134</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1196</v>
+        <v>1.0134</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1196</v>
+        <v>1.0134</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1196</v>
+        <v>1.0134</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1196</v>
+        <v>1.0134</v>
       </c>
       <c r="N26" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.0148</v>
+        <v>1.0055</v>
       </c>
       <c r="C27" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0929</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1622</v>
+        <v>-0.1477</v>
       </c>
       <c r="E27" t="n">
-        <v>1.0148</v>
+        <v>1.0055</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0148</v>
+        <v>1.0055</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0148</v>
+        <v>1.0055</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0148</v>
+        <v>1.0055</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.0148</v>
+        <v>1.0055</v>
       </c>
       <c r="N27" t="n">
         <v>182</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0086</v>
+        <v>0.8387</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0775</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1651</v>
+        <v>-0.2237</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0086</v>
+        <v>0.8387</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0086</v>
+        <v>0.8387</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0086</v>
+        <v>0.8387</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0086</v>
+        <v>0.8387</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0086</v>
+        <v>0.8387</v>
       </c>
       <c r="N28" t="n">
         <v>241</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9634</v>
+        <v>0.8274</v>
       </c>
       <c r="C29" t="n">
-        <v>0.089</v>
+        <v>0.0764</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1856</v>
+        <v>-0.2289</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9634</v>
+        <v>0.8274</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9634</v>
+        <v>0.8274</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9634</v>
+        <v>0.8274</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9634</v>
+        <v>0.8274</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9634</v>
+        <v>0.8274</v>
       </c>
       <c r="N29" t="n">
         <v>175</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5944</v>
+        <v>0.7143</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0549</v>
+        <v>0.066</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3536</v>
+        <v>-0.2804</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5944</v>
+        <v>0.7143</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1261</v>
+        <v>-1.0681</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4683</v>
+        <v>1.7824</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1261</v>
+        <v>-1.0681</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.5997</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4683</v>
+        <v>1.7824</v>
       </c>
       <c r="K30" t="n">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="L30" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5364</v>
+        <v>1.1827</v>
       </c>
       <c r="N30" t="n">
-        <v>291</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6636</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0514</v>
+        <v>0.0613</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3706</v>
+        <v>-0.3035</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6636</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.2019</v>
+        <v>0.2271</v>
       </c>
       <c r="G31" t="n">
-        <v>1.7588</v>
+        <v>0.4365</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.2019</v>
+        <v>0.2271</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.649</v>
+        <v>0.1275</v>
       </c>
       <c r="J31" t="n">
-        <v>1.7588</v>
+        <v>0.4365</v>
       </c>
       <c r="K31" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="L31" t="n">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1098</v>
+        <v>0.5640000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>235</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.3833</v>
+        <v>0.2233</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0354</v>
+        <v>0.0206</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4497</v>
+        <v>-0.5041</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3833</v>
+        <v>0.2233</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3833</v>
+        <v>0.2233</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3833</v>
+        <v>0.2233</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3833</v>
+        <v>0.2233</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3833</v>
+        <v>0.2233</v>
       </c>
       <c r="N32" t="n">
         <v>165</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0978</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0071</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.5612</v>
       </c>
       <c r="E33" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0978</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.4373</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.3395</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.4373</v>
       </c>
       <c r="I33" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.2456</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.3395</v>
       </c>
       <c r="K33" t="n">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M33" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.09390000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>165</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0113</v>
+        <v>0.0067</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6191</v>
+        <v>-0.6027</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0113</v>
+        <v>0.0067</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0113</v>
+        <v>0.0067</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0113</v>
+        <v>0.0067</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0113</v>
+        <v>0.0067</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0113</v>
+        <v>0.0067</v>
       </c>
       <c r="N34" t="n">
         <v>175</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0009</v>
+        <v>-0.0007</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6287</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3463</v>
+        <v>-0.008</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3562</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3463</v>
+        <v>-0.008</v>
       </c>
       <c r="I35" t="n">
-        <v>0.187</v>
+        <v>-0.008</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3562</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="L35" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1692</v>
+        <v>-0.008</v>
       </c>
       <c r="N35" t="n">
-        <v>275</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4347</v>
+        <v>-0.5092</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0401</v>
+        <v>-0.047</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.8378</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4347</v>
+        <v>-0.5092</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4347</v>
+        <v>-0.5092</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4347</v>
+        <v>-0.5092</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4347</v>
+        <v>-0.5092</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4347</v>
+        <v>-0.5092</v>
       </c>
       <c r="N36" t="n">
         <v>241</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8294</v>
+        <v>-0.8072</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0766</v>
+        <v>-0.0746</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0018</v>
+        <v>-0.9735</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8294</v>
+        <v>-0.8072</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8294</v>
+        <v>-0.8072</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8294</v>
+        <v>-0.8072</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8294</v>
+        <v>-0.8072</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8294</v>
+        <v>-0.8072</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9462</v>
+        <v>-0.9613</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0888</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0549</v>
+        <v>-1.0437</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9462</v>
+        <v>-0.9613</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9462</v>
+        <v>-0.9613</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9462</v>
+        <v>-0.9613</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9462</v>
+        <v>-0.9613</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9462</v>
+        <v>-0.9613</v>
       </c>
       <c r="N38" t="n">
         <v>182</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8529</v>
+        <v>-1.8475</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1711</v>
+        <v>-0.1706</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4677</v>
+        <v>-1.4474</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8529</v>
+        <v>-1.8475</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8529</v>
+        <v>-1.8475</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8529</v>
+        <v>-1.8475</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8529</v>
+        <v>-1.8475</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8529</v>
+        <v>-1.8475</v>
       </c>
       <c r="N39" t="n">
         <v>241</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0441</v>
+        <v>-2.1227</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1888</v>
+        <v>-0.1961</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5547</v>
+        <v>-1.5728</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0441</v>
+        <v>-2.1227</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0441</v>
+        <v>-2.1227</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0441</v>
+        <v>-2.1227</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0441</v>
+        <v>-2.1227</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0441</v>
+        <v>-2.1227</v>
       </c>
       <c r="N40" t="n">
         <v>182</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.295</v>
+        <v>-2.156</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.212</v>
+        <v>-0.1991</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6689</v>
+        <v>-1.5879</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.295</v>
+        <v>-2.156</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.295</v>
+        <v>-2.156</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.295</v>
+        <v>-2.156</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.295</v>
+        <v>-2.156</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.295</v>
+        <v>-2.156</v>
       </c>
       <c r="N41" t="n">
         <v>182</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3187</v>
+        <v>0.2713</v>
       </c>
       <c r="J2" t="n">
-        <v>7.6488</v>
+        <v>6.5112</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.96</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0562</v>
+        <v>-0.0455</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.3488</v>
+        <v>-1.092</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1553</v>
+        <v>-0.139</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.7272</v>
+        <v>-3.336</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3304</v>
+        <v>-0.3142</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.9296</v>
+        <v>-7.5408</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5254</v>
+        <v>-0.5283</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.6096</v>
+        <v>-12.6792</v>
       </c>
     </row>
     <row r="7">
@@ -2669,10 +2669,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0084</v>
+        <v>1.003</v>
       </c>
       <c r="J8" t="n">
-        <v>24.2016</v>
+        <v>24.072</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8572</v>
+        <v>0.8398</v>
       </c>
       <c r="J9" t="n">
-        <v>20.5728</v>
+        <v>20.1552</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4218</v>
+        <v>0.3895</v>
       </c>
       <c r="J10" t="n">
-        <v>10.1232</v>
+        <v>9.348000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1848</v>
+        <v>-0.1546</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.4352</v>
+        <v>-3.7104</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>0.745</v>
+        <v>0.6946</v>
       </c>
       <c r="J12" t="n">
-        <v>19.37</v>
+        <v>18.0596</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1525</v>
+        <v>-0.1335</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.965</v>
+        <v>-3.471</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1634</v>
+        <v>-0.1441</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.2484</v>
+        <v>-3.7466</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2754</v>
+        <v>-0.2562</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.1604</v>
+        <v>-6.6612</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.304</v>
+        <v>-0.2861</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.904</v>
+        <v>-7.4386</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3503</v>
+        <v>1.3852</v>
       </c>
       <c r="J17" t="n">
-        <v>35.1078</v>
+        <v>36.0152</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6761</v>
+        <v>0.644</v>
       </c>
       <c r="J18" t="n">
-        <v>17.5786</v>
+        <v>16.744</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3654</v>
+        <v>0.3305</v>
       </c>
       <c r="J19" t="n">
-        <v>9.500400000000001</v>
+        <v>8.593</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1426</v>
+        <v>0.1186</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7076</v>
+        <v>3.0836</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5505</v>
+        <v>-0.5122</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.313</v>
+        <v>-13.3172</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.33</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6381</v>
+        <v>0.5794</v>
       </c>
       <c r="J22" t="n">
-        <v>19.143</v>
+        <v>17.382</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.11</v>
       </c>
       <c r="I23" t="n">
-        <v>0.268</v>
+        <v>0.2204</v>
       </c>
       <c r="J23" t="n">
-        <v>8.039999999999999</v>
+        <v>6.612</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.97</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0598</v>
+        <v>-0.0467</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.794</v>
+        <v>-1.401</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0742</v>
+        <v>-0.0594</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.226</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.74</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3124</v>
+        <v>-0.2953</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.372</v>
+        <v>-8.859</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8993</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>26.979</v>
+        <v>26.448</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8598</v>
+        <v>0.8388</v>
       </c>
       <c r="J28" t="n">
-        <v>25.794</v>
+        <v>25.164</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.14</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4141</v>
+        <v>0.3783</v>
       </c>
       <c r="J29" t="n">
-        <v>12.423</v>
+        <v>11.349</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.08</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2616</v>
+        <v>0.2299</v>
       </c>
       <c r="J30" t="n">
-        <v>7.848</v>
+        <v>6.897</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3478</v>
+        <v>-0.3065</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.434</v>
+        <v>-9.195</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.4</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7269</v>
+        <v>0.6693</v>
       </c>
       <c r="J32" t="n">
-        <v>26.1684</v>
+        <v>24.0948</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3662</v>
+        <v>0.3127</v>
       </c>
       <c r="J33" t="n">
-        <v>13.1832</v>
+        <v>11.2572</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2023</v>
+        <v>0.1637</v>
       </c>
       <c r="J34" t="n">
-        <v>7.2828</v>
+        <v>5.8932</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0646</v>
+        <v>-0.0507</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.3256</v>
+        <v>-1.8252</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2597</v>
+        <v>-0.2405</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.3492</v>
+        <v>-8.657999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.35</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9042</v>
+        <v>0.888</v>
       </c>
       <c r="J37" t="n">
-        <v>32.5512</v>
+        <v>31.968</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3094</v>
+        <v>0.2694</v>
       </c>
       <c r="J38" t="n">
-        <v>11.1384</v>
+        <v>9.698399999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2353</v>
+        <v>-0.1976</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.470800000000001</v>
+        <v>-7.1136</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.9</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3472</v>
+        <v>-0.3048</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.4992</v>
+        <v>-10.9728</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4743</v>
+        <v>-0.4316</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.0748</v>
+        <v>-15.5376</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3211</v>
+        <v>0.269</v>
       </c>
       <c r="J42" t="n">
-        <v>9.632999999999999</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2223</v>
+        <v>0.1784</v>
       </c>
       <c r="J43" t="n">
-        <v>6.669</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0398</v>
+        <v>-0.0309</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.194</v>
+        <v>-0.927</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2071</v>
+        <v>-0.1868</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.213</v>
+        <v>-5.604</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3337</v>
+        <v>-0.3175</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.011</v>
+        <v>-9.525</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7726</v>
+        <v>0.7565</v>
       </c>
       <c r="J47" t="n">
-        <v>23.178</v>
+        <v>22.695</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.23</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5732</v>
+        <v>0.5626</v>
       </c>
       <c r="J48" t="n">
-        <v>17.196</v>
+        <v>16.878</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4573</v>
+        <v>0.4263</v>
       </c>
       <c r="J49" t="n">
-        <v>13.719</v>
+        <v>12.789</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2246</v>
+        <v>-0.1875</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.738</v>
+        <v>-5.625</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2246</v>
+        <v>-0.1875</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.738</v>
+        <v>-5.625</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5676</v>
+        <v>0.5323</v>
       </c>
       <c r="J52" t="n">
-        <v>15.3252</v>
+        <v>14.3721</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.32</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4316</v>
+        <v>0.3698</v>
       </c>
       <c r="J53" t="n">
-        <v>11.6532</v>
+        <v>9.9846</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.25</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3558</v>
+        <v>0.298</v>
       </c>
       <c r="J54" t="n">
-        <v>9.6066</v>
+        <v>8.045999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.04</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0745</v>
+        <v>0.0541</v>
       </c>
       <c r="J55" t="n">
-        <v>2.0115</v>
+        <v>1.4607</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0892</v>
+        <v>-0.0735</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.4084</v>
+        <v>-1.9845</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3263</v>
+        <v>0.317</v>
       </c>
       <c r="J57" t="n">
-        <v>8.8101</v>
+        <v>8.558999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.97</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0541</v>
+        <v>-0.0434</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.4607</v>
+        <v>-1.1718</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.95</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0819</v>
+        <v>-0.068</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.2113</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.246</v>
+        <v>-0.2261</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.642</v>
+        <v>-6.1047</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.285</v>
+        <v>-0.2662</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.695</v>
+        <v>-7.1874</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.84</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1932</v>
+        <v>-0.1769</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.6368</v>
+        <v>-4.2456</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2236</v>
+        <v>-0.2068</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.3664</v>
+        <v>-4.9632</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2427</v>
+        <v>-0.2257</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.8248</v>
+        <v>-5.4168</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.79</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2427</v>
+        <v>-0.2257</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.8248</v>
+        <v>-5.4168</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3349</v>
+        <v>-0.3194</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.037599999999999</v>
+        <v>-7.6656</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.79</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3196</v>
+        <v>1.3248</v>
       </c>
       <c r="J67" t="n">
-        <v>31.6704</v>
+        <v>31.7952</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6044</v>
+        <v>0.5969</v>
       </c>
       <c r="J68" t="n">
-        <v>14.5056</v>
+        <v>14.3256</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4216</v>
+        <v>0.3903</v>
       </c>
       <c r="J69" t="n">
-        <v>10.1184</v>
+        <v>9.3672</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3745</v>
+        <v>0.342</v>
       </c>
       <c r="J70" t="n">
-        <v>8.988</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0919</v>
+        <v>0.0713</v>
       </c>
       <c r="J71" t="n">
-        <v>2.2056</v>
+        <v>1.7112</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8647</v>
+        <v>0.852</v>
       </c>
       <c r="J72" t="n">
-        <v>25.941</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6469</v>
+        <v>0.6328</v>
       </c>
       <c r="J73" t="n">
-        <v>19.407</v>
+        <v>18.984</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4701</v>
+        <v>-0.4274</v>
       </c>
       <c r="J74" t="n">
-        <v>-14.103</v>
+        <v>-12.822</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.79</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6117</v>
+        <v>-0.5734</v>
       </c>
       <c r="J75" t="n">
-        <v>-18.351</v>
+        <v>-17.202</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.73</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.7158</v>
       </c>
       <c r="J76" t="n">
-        <v>-22.365</v>
+        <v>-21.474</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5997</v>
+        <v>0.571</v>
       </c>
       <c r="J77" t="n">
-        <v>17.991</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.32</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5556</v>
+        <v>0.529</v>
       </c>
       <c r="J78" t="n">
-        <v>16.668</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0585</v>
+        <v>0.0428</v>
       </c>
       <c r="J79" t="n">
-        <v>1.755</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0094</v>
+        <v>-0.007</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.282</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.97</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0543</v>
       </c>
       <c r="J81" t="n">
-        <v>-2.058</v>
+        <v>-1.629</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.79</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3317</v>
+        <v>1.3392</v>
       </c>
       <c r="J82" t="n">
-        <v>30.6291</v>
+        <v>30.8016</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6821</v>
+        <v>0.6696</v>
       </c>
       <c r="J83" t="n">
-        <v>15.6883</v>
+        <v>15.4008</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4054</v>
+        <v>0.3722</v>
       </c>
       <c r="J84" t="n">
-        <v>9.324199999999999</v>
+        <v>8.560600000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1949</v>
+        <v>0.1671</v>
       </c>
       <c r="J85" t="n">
-        <v>4.4827</v>
+        <v>3.8433</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5362</v>
+        <v>-0.4987</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.3326</v>
+        <v>-11.4701</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.08</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2386</v>
+        <v>0.194</v>
       </c>
       <c r="J87" t="n">
-        <v>5.4878</v>
+        <v>4.462</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.02</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0945</v>
+        <v>0.0692</v>
       </c>
       <c r="J88" t="n">
-        <v>2.1735</v>
+        <v>1.5916</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.01</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0634</v>
+        <v>0.0446</v>
       </c>
       <c r="J89" t="n">
-        <v>1.4582</v>
+        <v>1.0258</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1807</v>
+        <v>-0.1619</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.1561</v>
+        <v>-3.7237</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.44</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5644</v>
+        <v>-0.574</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.9812</v>
+        <v>-13.202</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.433</v>
+        <v>0.382</v>
       </c>
       <c r="J92" t="n">
-        <v>10.825</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1772</v>
+        <v>-0.16</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.43</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1876</v>
+        <v>-0.1701</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.69</v>
+        <v>-4.2525</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2364</v>
+        <v>-0.218</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.91</v>
+        <v>-5.45</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.47</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5344</v>
+        <v>-0.5386</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.36</v>
+        <v>-13.465</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.53</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1359</v>
+        <v>1.1485</v>
       </c>
       <c r="J97" t="n">
-        <v>28.3975</v>
+        <v>28.7125</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.35</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8439</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>21.0975</v>
+        <v>20.6025</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.35</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8439</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>21.0975</v>
+        <v>20.6025</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5185</v>
+        <v>0.4862</v>
       </c>
       <c r="J100" t="n">
-        <v>12.9625</v>
+        <v>12.155</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6325</v>
+        <v>-0.6004</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.8125</v>
+        <v>-15.01</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5921</v>
+        <v>0.5432</v>
       </c>
       <c r="J102" t="n">
-        <v>13.0262</v>
+        <v>11.9504</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0711</v>
+        <v>-0.0592</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.5642</v>
+        <v>-1.3024</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1877</v>
+        <v>-0.1702</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.1294</v>
+        <v>-3.7444</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3032</v>
+        <v>-0.2858</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.6704</v>
+        <v>-6.2876</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.37</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6191</v>
+        <v>-0.6373</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.6202</v>
+        <v>-14.0206</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.72</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3529</v>
+        <v>1.3751</v>
       </c>
       <c r="J107" t="n">
-        <v>29.7638</v>
+        <v>30.2522</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.72</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3529</v>
+        <v>1.3751</v>
       </c>
       <c r="J108" t="n">
-        <v>29.7638</v>
+        <v>30.2522</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.47</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0303</v>
+        <v>1.0377</v>
       </c>
       <c r="J109" t="n">
-        <v>22.6666</v>
+        <v>22.8294</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.06</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1682</v>
+        <v>0.1392</v>
       </c>
       <c r="J110" t="n">
-        <v>3.7004</v>
+        <v>3.0624</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0626</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.4322</v>
+        <v>-1.3772</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.71</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2966</v>
+        <v>-0.285</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.932</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2966</v>
+        <v>-0.285</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.932</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.63</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3704</v>
+        <v>-0.3611</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.408</v>
+        <v>-7.222</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.58</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4125</v>
+        <v>-0.4043</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.25</v>
+        <v>-8.086</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5265</v>
+        <v>-0.5276</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.53</v>
+        <v>-10.552</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1231</v>
+        <v>1.1381</v>
       </c>
       <c r="J117" t="n">
-        <v>22.462</v>
+        <v>22.762</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.53</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1101</v>
+        <v>1.1249</v>
       </c>
       <c r="J118" t="n">
-        <v>22.202</v>
+        <v>22.498</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9335</v>
+        <v>0.9285</v>
       </c>
       <c r="J119" t="n">
-        <v>18.67</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.36</v>
       </c>
       <c r="I120" t="n">
-        <v>0.843</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>16.86</v>
+        <v>16.622</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.18</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4721</v>
+        <v>0.442</v>
       </c>
       <c r="J121" t="n">
-        <v>9.442</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7817</v>
+        <v>0.8361</v>
       </c>
       <c r="J122" t="n">
-        <v>14.8523</v>
+        <v>15.8859</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.46</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.5064</v>
+        <v>-0.5059</v>
       </c>
       <c r="J123" t="n">
-        <v>-9.621600000000001</v>
+        <v>-9.6121</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.41</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5507</v>
+        <v>-0.5547</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.4633</v>
+        <v>-10.5393</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.31</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6402</v>
+        <v>-0.6576</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.1638</v>
+        <v>-12.4944</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.3</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6492</v>
+        <v>-0.6682</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.3348</v>
+        <v>-12.6958</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.86</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4996</v>
+        <v>1.5315</v>
       </c>
       <c r="J127" t="n">
-        <v>28.4924</v>
+        <v>29.0985</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.74</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3565</v>
+        <v>1.3808</v>
       </c>
       <c r="J128" t="n">
-        <v>25.7735</v>
+        <v>26.2352</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.51</v>
       </c>
       <c r="I129" t="n">
-        <v>1.0739</v>
+        <v>1.0911</v>
       </c>
       <c r="J129" t="n">
-        <v>20.4041</v>
+        <v>20.7309</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.4</v>
       </c>
       <c r="I130" t="n">
-        <v>0.9025</v>
+        <v>0.8998</v>
       </c>
       <c r="J130" t="n">
-        <v>17.1475</v>
+        <v>17.0962</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.13</v>
       </c>
       <c r="I131" t="n">
-        <v>0.336</v>
+        <v>0.302</v>
       </c>
       <c r="J131" t="n">
-        <v>6.384</v>
+        <v>5.738</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.91</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0774</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.0724</v>
+        <v>-1.7028</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.78</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2397</v>
+        <v>-0.2253</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.2734</v>
+        <v>-4.9566</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.77</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2497</v>
+        <v>-0.2355</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.4934</v>
+        <v>-5.181</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.48</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5092</v>
+        <v>-0.5085</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.2024</v>
+        <v>-11.187</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.47</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.518</v>
+        <v>-0.5183</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.396</v>
+        <v>-11.4026</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2764</v>
+        <v>1.2969</v>
       </c>
       <c r="J137" t="n">
-        <v>28.0808</v>
+        <v>28.5318</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.63</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2269</v>
+        <v>1.246</v>
       </c>
       <c r="J138" t="n">
-        <v>26.9918</v>
+        <v>27.412</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
-        <v>1.0887</v>
+        <v>1.1055</v>
       </c>
       <c r="J139" t="n">
-        <v>23.9514</v>
+        <v>24.321</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.48</v>
       </c>
       <c r="I140" t="n">
-        <v>1.0366</v>
+        <v>1.0487</v>
       </c>
       <c r="J140" t="n">
-        <v>22.8052</v>
+        <v>23.0714</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.366</v>
+        <v>0.333</v>
       </c>
       <c r="J141" t="n">
-        <v>8.052</v>
+        <v>7.326</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4939</v>
+        <v>0.4348</v>
       </c>
       <c r="J142" t="n">
-        <v>13.3353</v>
+        <v>11.7396</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3407</v>
+        <v>0.2876</v>
       </c>
       <c r="J143" t="n">
-        <v>9.1989</v>
+        <v>7.7652</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0412</v>
+        <v>0.0284</v>
       </c>
       <c r="J144" t="n">
-        <v>1.1124</v>
+        <v>0.7668</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0446</v>
+        <v>-0.0337</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.2042</v>
+        <v>-0.9099</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.76</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2939</v>
+        <v>-0.2758</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.9353</v>
+        <v>-7.4466</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.99</v>
       </c>
       <c r="I147" t="n">
-        <v>1.7584</v>
+        <v>1.8285</v>
       </c>
       <c r="J147" t="n">
-        <v>47.4768</v>
+        <v>49.3695</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.26</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6481</v>
       </c>
       <c r="J148" t="n">
-        <v>18.3843</v>
+        <v>17.4987</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3162</v>
+        <v>-0.2751</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.5374</v>
+        <v>-7.4277</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5462</v>
+        <v>-0.5072</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.7474</v>
+        <v>-13.6944</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.74</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7506</v>
+        <v>-0.7244</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.2662</v>
+        <v>-19.5588</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4238</v>
+        <v>0.3667</v>
       </c>
       <c r="J152" t="n">
-        <v>12.2902</v>
+        <v>10.6343</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3898</v>
+        <v>0.3343</v>
       </c>
       <c r="J153" t="n">
-        <v>11.3042</v>
+        <v>9.694699999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2829</v>
+        <v>0.2346</v>
       </c>
       <c r="J154" t="n">
-        <v>8.2041</v>
+        <v>6.8034</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.96</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0761</v>
+        <v>-0.0609</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.2069</v>
+        <v>-1.7661</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.77</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2858</v>
+        <v>-0.2675</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.2882</v>
+        <v>-7.7575</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.24</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6551</v>
+        <v>0.6192</v>
       </c>
       <c r="J157" t="n">
-        <v>18.9979</v>
+        <v>17.9568</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.19</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5437</v>
+        <v>0.5038</v>
       </c>
       <c r="J158" t="n">
-        <v>15.7673</v>
+        <v>14.6102</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.1</v>
       </c>
       <c r="I159" t="n">
-        <v>0.327</v>
+        <v>0.2885</v>
       </c>
       <c r="J159" t="n">
-        <v>9.483000000000001</v>
+        <v>8.3665</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2746</v>
+        <v>0.2387</v>
       </c>
       <c r="J160" t="n">
-        <v>7.9634</v>
+        <v>6.9223</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.77</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6711</v>
+        <v>-0.6373</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.4619</v>
+        <v>-18.4817</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.96</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0523</v>
+        <v>-0.0416</v>
       </c>
       <c r="J162" t="n">
-        <v>-1.2552</v>
+        <v>-0.9984</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.88</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1524</v>
+        <v>-0.1366</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.6576</v>
+        <v>-3.2784</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1635</v>
+        <v>-0.1473</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.924</v>
+        <v>-3.5352</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.78</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2531</v>
+        <v>-0.2355</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.0744</v>
+        <v>-5.652</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.52</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4884</v>
+        <v>-0.4861</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.7216</v>
+        <v>-11.6664</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.66</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3027</v>
+        <v>1.3223</v>
       </c>
       <c r="J167" t="n">
-        <v>31.2648</v>
+        <v>31.7352</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.32</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7816</v>
+        <v>0.759</v>
       </c>
       <c r="J168" t="n">
-        <v>18.7584</v>
+        <v>18.216</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.26</v>
       </c>
       <c r="I169" t="n">
-        <v>0.6634</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J169" t="n">
-        <v>15.9216</v>
+        <v>15.2544</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.15</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4236</v>
+        <v>0.3911</v>
       </c>
       <c r="J170" t="n">
-        <v>10.1664</v>
+        <v>9.3864</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2791</v>
+        <v>-0.2421</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.6984</v>
+        <v>-5.8104</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0117</v>
+        <v>0.9557</v>
       </c>
       <c r="J172" t="n">
-        <v>17.1989</v>
+        <v>16.2469</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.71</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7739</v>
+        <v>0.7076</v>
       </c>
       <c r="J173" t="n">
-        <v>13.1563</v>
+        <v>12.0292</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.6</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6772</v>
+        <v>0.6126</v>
       </c>
       <c r="J174" t="n">
-        <v>11.5124</v>
+        <v>10.4142</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.6</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6772</v>
+        <v>0.6126</v>
       </c>
       <c r="J175" t="n">
-        <v>11.5124</v>
+        <v>10.4142</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.54</v>
       </c>
       <c r="I176" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5582</v>
       </c>
       <c r="J176" t="n">
-        <v>10.5655</v>
+        <v>9.4894</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.82</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1515</v>
+        <v>-0.1249</v>
       </c>
       <c r="J177" t="n">
-        <v>-2.5755</v>
+        <v>-2.1233</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.7</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2841</v>
+        <v>-0.2709</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.8297</v>
+        <v>-4.6053</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.67</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3147</v>
+        <v>-0.3043</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.3499</v>
+        <v>-5.1731</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.26</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6831</v>
+        <v>-0.7084</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.6127</v>
+        <v>-12.0428</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.19</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7466</v>
+        <v>-0.7861</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.6922</v>
+        <v>-13.3637</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.54</v>
       </c>
       <c r="I182" t="n">
-        <v>0.924</v>
+        <v>0.877</v>
       </c>
       <c r="J182" t="n">
-        <v>55.44</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.06</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1605</v>
+        <v>0.1275</v>
       </c>
       <c r="J183" t="n">
-        <v>9.630000000000001</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1153</v>
+        <v>0.0892</v>
       </c>
       <c r="J184" t="n">
-        <v>6.918</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1065</v>
+        <v>-0.0887</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.39</v>
+        <v>-5.322</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.88</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1772</v>
+        <v>-0.1568</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.632</v>
+        <v>-9.407999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.17</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5056</v>
+        <v>0.4641</v>
       </c>
       <c r="J187" t="n">
-        <v>30.336</v>
+        <v>27.846</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3328</v>
+        <v>0.2925</v>
       </c>
       <c r="J188" t="n">
-        <v>19.968</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0056</v>
+        <v>-0.0032</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.336</v>
+        <v>-0.192</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.98</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1063</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.378</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1762</v>
+        <v>-0.143</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.572</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.43</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7875</v>
+        <v>0.7341</v>
       </c>
       <c r="J192" t="n">
-        <v>26.775</v>
+        <v>24.9594</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4513</v>
       </c>
       <c r="J193" t="n">
-        <v>17.3604</v>
+        <v>15.3442</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.93</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1136</v>
+        <v>-0.0955</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.8624</v>
+        <v>-3.247</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1376</v>
+        <v>-0.1182</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.6784</v>
+        <v>-4.0188</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.61</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4306</v>
+        <v>-0.4239</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.6404</v>
+        <v>-14.4126</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.47</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0718</v>
+        <v>1.0803</v>
       </c>
       <c r="J197" t="n">
-        <v>36.4412</v>
+        <v>36.7302</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.34</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8428</v>
+        <v>0.8202</v>
       </c>
       <c r="J198" t="n">
-        <v>28.6552</v>
+        <v>27.8868</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4389</v>
+        <v>0.4021</v>
       </c>
       <c r="J199" t="n">
-        <v>14.9226</v>
+        <v>13.6714</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.318</v>
+        <v>-0.2771</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.812</v>
+        <v>-9.4214</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3456</v>
+        <v>-0.3041</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.7504</v>
+        <v>-10.3394</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.25</v>
       </c>
       <c r="I202" t="n">
-        <v>0.498</v>
+        <v>0.5334</v>
       </c>
       <c r="J202" t="n">
-        <v>10.458</v>
+        <v>11.2014</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.9</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1154</v>
+        <v>-0.0998</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.4234</v>
+        <v>-2.0958</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.65</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3637</v>
+        <v>-0.3506</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.6377</v>
+        <v>-7.3626</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.43</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5574</v>
+        <v>-0.5636</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.7054</v>
+        <v>-11.8356</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.37</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.609</v>
+        <v>-0.6237</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.789</v>
+        <v>-13.0977</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.7</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7834</v>
+        <v>0.7125</v>
       </c>
       <c r="J207" t="n">
-        <v>16.4514</v>
+        <v>14.9625</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.6</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6209</v>
       </c>
       <c r="J208" t="n">
-        <v>14.511</v>
+        <v>13.0389</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.38</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4795</v>
+        <v>0.4182</v>
       </c>
       <c r="J209" t="n">
-        <v>10.0695</v>
+        <v>8.7822</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.36</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4589</v>
+        <v>0.3987</v>
       </c>
       <c r="J210" t="n">
-        <v>9.636900000000001</v>
+        <v>8.3727</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.25</v>
       </c>
       <c r="I211" t="n">
-        <v>0.3384</v>
+        <v>0.2863</v>
       </c>
       <c r="J211" t="n">
-        <v>7.1064</v>
+        <v>6.0123</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.4</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9755</v>
+        <v>0.9681</v>
       </c>
       <c r="J212" t="n">
-        <v>27.314</v>
+        <v>27.1068</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3982</v>
+        <v>0.359</v>
       </c>
       <c r="J213" t="n">
-        <v>11.1496</v>
+        <v>10.052</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.06</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2162</v>
+        <v>0.1851</v>
       </c>
       <c r="J214" t="n">
-        <v>6.0536</v>
+        <v>5.1828</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2162</v>
+        <v>0.1851</v>
       </c>
       <c r="J215" t="n">
-        <v>6.0536</v>
+        <v>5.1828</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.489</v>
+        <v>-0.4473</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.692</v>
+        <v>-12.5244</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5684</v>
+        <v>0.5094</v>
       </c>
       <c r="J217" t="n">
-        <v>15.9152</v>
+        <v>14.2632</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.22</v>
       </c>
       <c r="I218" t="n">
-        <v>0.47</v>
+        <v>0.4116</v>
       </c>
       <c r="J218" t="n">
-        <v>13.16</v>
+        <v>11.5248</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1107</v>
+        <v>-0.0931</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.0996</v>
+        <v>-2.6068</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.77</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2809</v>
+        <v>-0.262</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.8652</v>
+        <v>-7.336</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.75</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3</v>
+        <v>-0.2821</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.4</v>
+        <v>-7.8988</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.63</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3035</v>
+        <v>1.3269</v>
       </c>
       <c r="J222" t="n">
-        <v>53.4435</v>
+        <v>54.4029</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.21</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5798</v>
+        <v>0.5422</v>
       </c>
       <c r="J223" t="n">
-        <v>23.7718</v>
+        <v>22.2302</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2424</v>
+        <v>0.2102</v>
       </c>
       <c r="J224" t="n">
-        <v>9.9384</v>
+        <v>8.6182</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.222</v>
+        <v>-0.1849</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.102</v>
+        <v>-7.5809</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7883</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="J226" t="n">
-        <v>-32.3203</v>
+        <v>-31.3486</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.52</v>
       </c>
       <c r="I227" t="n">
-        <v>0.9031</v>
+        <v>0.8551</v>
       </c>
       <c r="J227" t="n">
-        <v>37.0271</v>
+        <v>35.0591</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.12</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2795</v>
+        <v>0.2322</v>
       </c>
       <c r="J228" t="n">
-        <v>11.4595</v>
+        <v>9.520200000000001</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0635</v>
+        <v>-0.0497</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.6035</v>
+        <v>-2.0377</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1414</v>
+        <v>-0.1217</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.7974</v>
+        <v>-4.9897</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2284</v>
+        <v>-0.2081</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.3644</v>
+        <v>-8.5321</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.76</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2493</v>
+        <v>-0.2355</v>
       </c>
       <c r="J232" t="n">
-        <v>-4.986</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.7</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3085</v>
+        <v>-0.2971</v>
       </c>
       <c r="J233" t="n">
-        <v>-6.17</v>
+        <v>-5.942</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.59</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4053</v>
+        <v>-0.3965</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.106</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.58</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.414</v>
+        <v>-0.4055</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.279999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.51</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4754</v>
+        <v>-0.4711</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.507999999999999</v>
+        <v>-9.422000000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.62</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7104</v>
+        <v>0.6399</v>
       </c>
       <c r="J237" t="n">
-        <v>14.208</v>
+        <v>12.798</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.62</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7104</v>
+        <v>0.6399</v>
       </c>
       <c r="J238" t="n">
-        <v>14.208</v>
+        <v>12.798</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.53</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6256</v>
+        <v>0.5572</v>
       </c>
       <c r="J239" t="n">
-        <v>12.512</v>
+        <v>11.144</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.37</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4698</v>
+        <v>0.4089</v>
       </c>
       <c r="J240" t="n">
-        <v>9.396000000000001</v>
+        <v>8.178000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.11</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1628</v>
+        <v>0.1273</v>
       </c>
       <c r="J241" t="n">
-        <v>3.256</v>
+        <v>2.546</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.51</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1571</v>
+        <v>1.1741</v>
       </c>
       <c r="J242" t="n">
-        <v>39.3414</v>
+        <v>39.9194</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.18</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5259</v>
+        <v>0.4851</v>
       </c>
       <c r="J243" t="n">
-        <v>17.8806</v>
+        <v>16.4934</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0518</v>
+        <v>0.0389</v>
       </c>
       <c r="J244" t="n">
-        <v>1.7612</v>
+        <v>1.3226</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5754</v>
+        <v>-0.5359</v>
       </c>
       <c r="J245" t="n">
-        <v>-19.5636</v>
+        <v>-18.2206</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.76</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6892</v>
+        <v>-0.6561</v>
       </c>
       <c r="J246" t="n">
-        <v>-23.4328</v>
+        <v>-22.3074</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.2</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4258</v>
+        <v>0.3686</v>
       </c>
       <c r="J247" t="n">
-        <v>14.4772</v>
+        <v>12.5324</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.227</v>
+        <v>0.1839</v>
       </c>
       <c r="J248" t="n">
-        <v>7.718</v>
+        <v>6.2526</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1865</v>
+        <v>0.1482</v>
       </c>
       <c r="J249" t="n">
-        <v>6.341</v>
+        <v>5.0388</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1019</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.4646</v>
+        <v>-2.873</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.88</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1725</v>
+        <v>-0.152</v>
       </c>
       <c r="J251" t="n">
-        <v>-5.865</v>
+        <v>-5.168</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.37</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9003</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="J252" t="n">
-        <v>26.1087</v>
+        <v>25.5954</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.34</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8408</v>
+        <v>0.8183</v>
       </c>
       <c r="J253" t="n">
-        <v>24.3832</v>
+        <v>23.7307</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.16</v>
       </c>
       <c r="I254" t="n">
-        <v>0.4608</v>
+        <v>0.4244</v>
       </c>
       <c r="J254" t="n">
-        <v>13.3632</v>
+        <v>12.3076</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.11</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3413</v>
+        <v>0.3067</v>
       </c>
       <c r="J255" t="n">
-        <v>9.8977</v>
+        <v>8.894299999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.85</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5013</v>
+        <v>-0.461</v>
       </c>
       <c r="J256" t="n">
-        <v>-14.5377</v>
+        <v>-13.369</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.679</v>
+        <v>0.6224</v>
       </c>
       <c r="J257" t="n">
-        <v>19.691</v>
+        <v>18.0496</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2742</v>
+        <v>0.2256</v>
       </c>
       <c r="J258" t="n">
-        <v>7.9518</v>
+        <v>6.5424</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.92</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1226</v>
+        <v>-0.1043</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.5554</v>
+        <v>-3.0247</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.9</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1459</v>
+        <v>-0.1264</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.2311</v>
+        <v>-3.6656</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.66</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.383</v>
+        <v>-0.371</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.107</v>
+        <v>-10.759</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.56</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6861</v>
+        <v>0.6141</v>
       </c>
       <c r="J262" t="n">
-        <v>16.4664</v>
+        <v>14.7384</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.27</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3797</v>
+        <v>0.3194</v>
       </c>
       <c r="J263" t="n">
-        <v>9.1128</v>
+        <v>7.6656</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3108</v>
+        <v>0.2571</v>
       </c>
       <c r="J264" t="n">
-        <v>7.4592</v>
+        <v>6.1704</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0143</v>
+        <v>-0.0117</v>
       </c>
       <c r="J265" t="n">
-        <v>-0.3432</v>
+        <v>-0.2808</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.95</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1018</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>-2.4432</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.01</v>
       </c>
       <c r="I267" t="n">
-        <v>0.0531</v>
+        <v>0.0428</v>
       </c>
       <c r="J267" t="n">
-        <v>1.2744</v>
+        <v>1.0272</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1</v>
       </c>
       <c r="I268" t="n">
-        <v>0.0181</v>
+        <v>0.0155</v>
       </c>
       <c r="J268" t="n">
-        <v>0.4344</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1997</v>
+        <v>-0.1809</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.7928</v>
+        <v>-4.3416</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2395</v>
+        <v>-0.2203</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.748</v>
+        <v>-5.2872</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.67</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.362</v>
+        <v>-0.3476</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.688000000000001</v>
+        <v>-8.3424</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7121</v>
       </c>
       <c r="J272" t="n">
-        <v>22.1444</v>
+        <v>20.6509</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.01</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0478</v>
+        <v>0.0319</v>
       </c>
       <c r="J273" t="n">
-        <v>1.3862</v>
+        <v>0.9251</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.91</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1324</v>
+        <v>-0.1139</v>
       </c>
       <c r="J274" t="n">
-        <v>-3.8396</v>
+        <v>-3.3031</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.85</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1982</v>
+        <v>-0.1778</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.7478</v>
+        <v>-5.1562</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.65</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3899</v>
+        <v>-0.3783</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.3071</v>
+        <v>-10.9707</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.5</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1047</v>
+        <v>1.1161</v>
       </c>
       <c r="J277" t="n">
-        <v>32.0363</v>
+        <v>32.3669</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.7936</v>
+        <v>0.7688</v>
       </c>
       <c r="J278" t="n">
-        <v>23.0144</v>
+        <v>22.2952</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5665</v>
+        <v>0.5327</v>
       </c>
       <c r="J279" t="n">
-        <v>16.4285</v>
+        <v>15.4483</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.1045</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>3.0305</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.93</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2968</v>
+        <v>-0.2573</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.607200000000001</v>
+        <v>-7.4617</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5955</v>
+        <v>0.5687</v>
       </c>
       <c r="J282" t="n">
-        <v>13.101</v>
+        <v>12.5114</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.74</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2812</v>
+        <v>-0.2672</v>
       </c>
       <c r="J283" t="n">
-        <v>-6.1864</v>
+        <v>-5.8784</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3259</v>
+        <v>-0.3124</v>
       </c>
       <c r="J284" t="n">
-        <v>-7.1698</v>
+        <v>-6.8728</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.48</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5113</v>
+        <v>-0.5109</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.2486</v>
+        <v>-11.2398</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.36</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6153</v>
+        <v>-0.6307</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.5366</v>
+        <v>-13.8754</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1023</v>
+        <v>1.1158</v>
       </c>
       <c r="J287" t="n">
-        <v>24.2506</v>
+        <v>24.5476</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0758</v>
+        <v>1.0875</v>
       </c>
       <c r="J288" t="n">
-        <v>23.6676</v>
+        <v>23.925</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.45</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0039</v>
+        <v>1.0063</v>
       </c>
       <c r="J289" t="n">
-        <v>22.0858</v>
+        <v>22.1386</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.31</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7518</v>
+        <v>0.7327</v>
       </c>
       <c r="J290" t="n">
-        <v>16.5396</v>
+        <v>16.1194</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1108</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>2.4376</v>
+        <v>1.892</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.53</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1509</v>
+        <v>1.1642</v>
       </c>
       <c r="J292" t="n">
-        <v>32.2252</v>
+        <v>32.5976</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0676</v>
+        <v>1.0755</v>
       </c>
       <c r="J293" t="n">
-        <v>29.8928</v>
+        <v>30.114</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.07</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2327</v>
+        <v>0.2025</v>
       </c>
       <c r="J294" t="n">
-        <v>6.5156</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.98</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1306</v>
+        <v>-0.1033</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.6568</v>
+        <v>-2.8924</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.83</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5512</v>
+        <v>-0.513</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.4336</v>
+        <v>-14.364</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.3</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6282</v>
+        <v>0.5742</v>
       </c>
       <c r="J297" t="n">
-        <v>17.5896</v>
+        <v>16.0776</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4598</v>
+        <v>0.4038</v>
       </c>
       <c r="J298" t="n">
-        <v>12.8744</v>
+        <v>11.3064</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2336</v>
+        <v>-0.2138</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.5408</v>
+        <v>-5.9864</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.7</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3388</v>
+        <v>-0.3229</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.4864</v>
+        <v>-9.0412</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.52</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4985</v>
+        <v>-0.4987</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.958</v>
+        <v>-13.9636</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.5</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1307</v>
+        <v>1.1449</v>
       </c>
       <c r="J302" t="n">
-        <v>40.7052</v>
+        <v>41.2164</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.36</v>
       </c>
       <c r="I303" t="n">
-        <v>0.901</v>
+        <v>0.883</v>
       </c>
       <c r="J303" t="n">
-        <v>32.436</v>
+        <v>31.788</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.02</v>
       </c>
       <c r="I304" t="n">
-        <v>0.0862</v>
+        <v>0.0682</v>
       </c>
       <c r="J304" t="n">
-        <v>3.1032</v>
+        <v>2.4552</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4632</v>
+        <v>-0.4209</v>
       </c>
       <c r="J305" t="n">
-        <v>-16.6752</v>
+        <v>-15.1524</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7627</v>
+        <v>-0.7362</v>
       </c>
       <c r="J306" t="n">
-        <v>-27.4572</v>
+        <v>-26.5032</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.22</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4601</v>
+        <v>0.4017</v>
       </c>
       <c r="J307" t="n">
-        <v>16.5636</v>
+        <v>14.4612</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.06</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1658</v>
+        <v>0.1301</v>
       </c>
       <c r="J308" t="n">
-        <v>5.9688</v>
+        <v>4.6836</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1439</v>
+        <v>0.1114</v>
       </c>
       <c r="J309" t="n">
-        <v>5.1804</v>
+        <v>4.0104</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.99</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.0273</v>
+        <v>-0.0193</v>
       </c>
       <c r="J310" t="n">
-        <v>-0.9828</v>
+        <v>-0.6948</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.84</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2148</v>
+        <v>-0.1942</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.7328</v>
+        <v>-6.9912</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.31</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7994</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J312" t="n">
-        <v>23.982</v>
+        <v>23.181</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.471</v>
+        <v>0.4308</v>
       </c>
       <c r="J313" t="n">
-        <v>14.13</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2458</v>
+        <v>0.2124</v>
       </c>
       <c r="J314" t="n">
-        <v>7.374</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.01</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0454</v>
+        <v>0.034</v>
       </c>
       <c r="J315" t="n">
-        <v>1.362</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.91</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3332</v>
+        <v>-0.2911</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.996</v>
+        <v>-8.733000000000001</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.32</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6373</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J317" t="n">
-        <v>19.119</v>
+        <v>17.403</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2379</v>
+        <v>0.1925</v>
       </c>
       <c r="J318" t="n">
-        <v>7.137</v>
+        <v>5.775</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.89</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1558</v>
+        <v>-0.1361</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.674</v>
+        <v>-4.083</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.78</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2695</v>
+        <v>-0.2501</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.085000000000001</v>
+        <v>-7.503</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.78</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2695</v>
+        <v>-0.2501</v>
       </c>
       <c r="J321" t="n">
-        <v>-8.085000000000001</v>
+        <v>-7.503</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.5</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0727</v>
+        <v>1.0849</v>
       </c>
       <c r="J322" t="n">
-        <v>24.6721</v>
+        <v>24.9527</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.43</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9688</v>
+        <v>0.9674</v>
       </c>
       <c r="J323" t="n">
-        <v>22.2824</v>
+        <v>22.2502</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.42</v>
       </c>
       <c r="I324" t="n">
-        <v>0.952</v>
+        <v>0.9484</v>
       </c>
       <c r="J324" t="n">
-        <v>21.896</v>
+        <v>21.8132</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.37</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8633</v>
+        <v>0.8519</v>
       </c>
       <c r="J325" t="n">
-        <v>19.8559</v>
+        <v>19.5937</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.22</v>
       </c>
       <c r="I326" t="n">
-        <v>0.5632</v>
+        <v>0.5361</v>
       </c>
       <c r="J326" t="n">
-        <v>12.9536</v>
+        <v>12.3303</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.02</v>
       </c>
       <c r="I327" t="n">
-        <v>0.136</v>
+        <v>0.1128</v>
       </c>
       <c r="J327" t="n">
-        <v>3.128</v>
+        <v>2.5944</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.22</v>
+        <v>-0.2041</v>
       </c>
       <c r="J328" t="n">
-        <v>-5.06</v>
+        <v>-4.6943</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.73</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.295</v>
+        <v>-0.2792</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.785</v>
+        <v>-6.4216</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.7</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3223</v>
+        <v>-0.3069</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.4129</v>
+        <v>-7.0587</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.5</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5003</v>
+        <v>-0.499</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.5069</v>
+        <v>-11.477</v>
       </c>
     </row>
   </sheetData>
